--- a/BITACORA 2_ DIEGO_TAPIA_SALAZAR.xlsx
+++ b/BITACORA 2_ DIEGO_TAPIA_SALAZAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santiago Castañeda\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c3d00bcd4006f853/Desktop/DUKITO DOC/SENA_PR/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{8E818715-0928-484B-A41A-0DCEADF6C08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bitacora" sheetId="6" r:id="rId1"/>
@@ -768,7 +768,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2632,7 +2632,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2820,163 +2820,193 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="116" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="116" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="122" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="121" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2988,166 +3018,112 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="88" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="69" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3177,7 +3153,25 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3232,177 +3226,360 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="88" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="69" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3421,188 +3598,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="116" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="116" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="121" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="122" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3610,6 +3607,34 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE1EF57"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2ED51"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3720,13 +3745,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -3736,6 +3754,13 @@
         <top style="medium">
           <color rgb="FFCCCCCC"/>
         </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FFCCCCCC"/>
         </bottom>
@@ -3769,34 +3794,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE1EF57"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2ED51"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4220,12 +4217,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{99010CAF-386D-41BE-AE72-8D38EFA83A09}" name="TablaSena" displayName="TablaSena" ref="A1:C39" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{99010CAF-386D-41BE-AE72-8D38EFA83A09}" name="TablaSena" displayName="TablaSena" ref="A1:C39" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:C39" xr:uid="{99010CAF-386D-41BE-AE72-8D38EFA83A09}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{61F34070-348E-42B3-BF87-5A1CD2BB6FD7}" name="PROGRAMA" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{7B4CB996-89B6-45DE-A53A-D02152366731}" name="COMPETENCIA" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{529DD12A-961C-42BF-9AA1-50D419FC6C5E}" name="RESULTADO DE APRENDIZAJE (RAP)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{61F34070-348E-42B3-BF87-5A1CD2BB6FD7}" name="PROGRAMA" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{7B4CB996-89B6-45DE-A53A-D02152366731}" name="COMPETENCIA" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{529DD12A-961C-42BF-9AA1-50D419FC6C5E}" name="RESULTADO DE APRENDIZAJE (RAP)" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4522,34 +4519,34 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB114"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="30" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="39.5546875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="9" customWidth="1"/>
     <col min="5" max="5" width="20" style="30" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" style="30" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="33.5703125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="22.5546875" style="30" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="33.5546875" style="9" customWidth="1"/>
     <col min="9" max="9" width="55" style="9" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" style="9" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" style="9" hidden="1" customWidth="1"/>
-    <col min="12" max="17" width="5.7109375" style="9" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="4.7109375" style="9" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="5.85546875" style="9" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="7.42578125" style="9" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="7.140625" style="9" hidden="1" customWidth="1"/>
-    <col min="22" max="23" width="5.7109375" style="9" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" style="9" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" style="9" hidden="1" customWidth="1"/>
+    <col min="12" max="17" width="5.6640625" style="9" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="4.6640625" style="9" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="5.88671875" style="9" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="7.44140625" style="9" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="7.109375" style="9" hidden="1" customWidth="1"/>
+    <col min="22" max="23" width="5.6640625" style="9" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="5" style="9" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="6.42578125" style="9" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="8.140625" style="9" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="5.140625" style="9" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="24.42578125" style="8" hidden="1" customWidth="1"/>
-    <col min="29" max="16384" width="11.42578125" style="7" hidden="1"/>
+    <col min="25" max="25" width="6.44140625" style="9" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="8.109375" style="9" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="5.109375" style="9" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="24.44140625" style="8" hidden="1" customWidth="1"/>
+    <col min="29" max="16384" width="11.44140625" style="7" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="29.25" customHeight="1">
+    <row r="1" spans="2:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="21"/>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
@@ -4580,14 +4577,14 @@
       <c r="AA1" s="7"/>
       <c r="AB1" s="7"/>
     </row>
-    <row r="2" spans="2:28" ht="29.25" customHeight="1">
+    <row r="2" spans="2:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="24"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
       <c r="I2" s="25" t="s">
         <v>1</v>
       </c>
@@ -4611,17 +4608,17 @@
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
     </row>
-    <row r="3" spans="2:28" ht="24" customHeight="1">
-      <c r="B3" s="171" t="s">
+    <row r="3" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="173"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="165"/>
       <c r="J3" s="8"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -4642,17 +4639,17 @@
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
     </row>
-    <row r="4" spans="2:28" ht="24" customHeight="1">
-      <c r="B4" s="177" t="s">
+    <row r="4" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="169" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="178"/>
-      <c r="I4" s="179"/>
+      <c r="C4" s="170"/>
+      <c r="D4" s="170"/>
+      <c r="E4" s="170"/>
+      <c r="F4" s="170"/>
+      <c r="G4" s="170"/>
+      <c r="H4" s="170"/>
+      <c r="I4" s="171"/>
       <c r="J4" s="8"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -4673,17 +4670,17 @@
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
     </row>
-    <row r="5" spans="2:28" ht="24" customHeight="1">
-      <c r="B5" s="174" t="s">
+    <row r="5" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="175"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="175"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="175"/>
-      <c r="I5" s="176"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="168"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="7"/>
@@ -4704,17 +4701,17 @@
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
     </row>
-    <row r="6" spans="2:28" ht="24" customHeight="1">
-      <c r="B6" s="177" t="s">
+    <row r="6" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="178"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="179"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="170"/>
+      <c r="E6" s="170"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="171"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="7"/>
@@ -4735,17 +4732,17 @@
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
     </row>
-    <row r="7" spans="2:28" ht="24" customHeight="1">
-      <c r="B7" s="174" t="s">
+    <row r="7" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="175"/>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="176"/>
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="167"/>
+      <c r="H7" s="167"/>
+      <c r="I7" s="168"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
@@ -4766,22 +4763,22 @@
       <c r="AA7" s="7"/>
       <c r="AB7" s="7"/>
     </row>
-    <row r="8" spans="2:28" ht="36.75" customHeight="1">
+    <row r="8" spans="2:28" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="184" t="b">
+      <c r="C8" s="182" t="b">
         <v>0</v>
       </c>
-      <c r="D8" s="185"/>
-      <c r="E8" s="186" t="s">
+      <c r="D8" s="183"/>
+      <c r="E8" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="187"/>
+      <c r="F8" s="185"/>
       <c r="G8" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="65" t="s">
+      <c r="H8" s="64" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="49" t="b">
@@ -4807,15 +4804,15 @@
       <c r="AA8" s="7"/>
       <c r="AB8" s="7"/>
     </row>
-    <row r="9" spans="2:28" ht="9" customHeight="1">
-      <c r="B9" s="67"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
+    <row r="9" spans="2:28" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="66"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
-      <c r="G9" s="198"/>
-      <c r="H9" s="198"/>
-      <c r="I9" s="64"/>
+      <c r="G9" s="193"/>
+      <c r="H9" s="193"/>
+      <c r="I9" s="63"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -4836,19 +4833,19 @@
       <c r="AA9" s="7"/>
       <c r="AB9" s="7"/>
     </row>
-    <row r="10" spans="2:28" ht="21" customHeight="1">
-      <c r="B10" s="165" t="s">
+    <row r="10" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="166"/>
-      <c r="D10" s="142"/>
-      <c r="E10" s="163" t="s">
+      <c r="C10" s="177"/>
+      <c r="D10" s="178"/>
+      <c r="E10" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="163"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="163"/>
-      <c r="I10" s="163"/>
+      <c r="F10" s="172"/>
+      <c r="G10" s="172"/>
+      <c r="H10" s="172"/>
+      <c r="I10" s="172"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
@@ -4869,19 +4866,19 @@
       <c r="AA10" s="7"/>
       <c r="AB10" s="7"/>
     </row>
-    <row r="11" spans="2:28" ht="21" customHeight="1">
-      <c r="B11" s="195">
+    <row r="11" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="162">
         <v>1</v>
       </c>
-      <c r="C11" s="196"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="194" t="s">
+      <c r="C11" s="155"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="192" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="194"/>
-      <c r="G11" s="194"/>
-      <c r="H11" s="194"/>
-      <c r="I11" s="194"/>
+      <c r="F11" s="192"/>
+      <c r="G11" s="192"/>
+      <c r="H11" s="192"/>
+      <c r="I11" s="192"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
@@ -4902,15 +4899,15 @@
       <c r="AA11" s="7"/>
       <c r="AB11" s="7"/>
     </row>
-    <row r="12" spans="2:28" ht="9" customHeight="1">
-      <c r="B12" s="67"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
+    <row r="12" spans="2:28" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="66"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
-      <c r="G12" s="198"/>
-      <c r="H12" s="198"/>
-      <c r="I12" s="64"/>
+      <c r="G12" s="193"/>
+      <c r="H12" s="193"/>
+      <c r="I12" s="63"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -4931,17 +4928,17 @@
       <c r="AA12" s="7"/>
       <c r="AB12" s="7"/>
     </row>
-    <row r="13" spans="2:28" ht="19.5" customHeight="1" thickBot="1">
-      <c r="B13" s="192" t="s">
+    <row r="13" spans="2:28" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="190" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="192"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="192"/>
-      <c r="F13" s="192"/>
-      <c r="G13" s="192"/>
-      <c r="H13" s="192"/>
-      <c r="I13" s="193"/>
+      <c r="C13" s="190"/>
+      <c r="D13" s="190"/>
+      <c r="E13" s="190"/>
+      <c r="F13" s="190"/>
+      <c r="G13" s="190"/>
+      <c r="H13" s="190"/>
+      <c r="I13" s="191"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -4962,60 +4959,41 @@
       <c r="AA13" s="7"/>
       <c r="AB13" s="7"/>
     </row>
-    <row r="14" spans="2:28" s="9" customFormat="1" ht="21" customHeight="1">
-      <c r="B14" s="165" t="s">
+    <row r="14" spans="2:28" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="176" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="166"/>
-      <c r="D14" s="142"/>
+      <c r="C14" s="177"/>
+      <c r="D14" s="178"/>
       <c r="E14" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="188" t="s">
+      <c r="F14" s="186" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="189"/>
-      <c r="H14" s="163" t="s">
+      <c r="G14" s="187"/>
+      <c r="H14" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="143"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61"/>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="61"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="61"/>
-      <c r="T14" s="61"/>
-      <c r="U14" s="61"/>
-      <c r="V14" s="61"/>
-      <c r="W14" s="61"/>
-      <c r="X14" s="61"/>
-      <c r="Y14" s="61"/>
-      <c r="Z14" s="61"/>
-      <c r="AA14" s="61"/>
-      <c r="AB14" s="61"/>
-    </row>
-    <row r="15" spans="2:28" ht="18" customHeight="1" thickBot="1">
-      <c r="B15" s="181" t="s">
+      <c r="I14" s="173"/>
+    </row>
+    <row r="15" spans="2:28" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="179" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="182"/>
-      <c r="D15" s="183"/>
+      <c r="C15" s="180"/>
+      <c r="D15" s="181"/>
       <c r="E15" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="190">
+      <c r="F15" s="188">
         <v>1030594222</v>
       </c>
-      <c r="G15" s="191"/>
-      <c r="H15" s="130">
+      <c r="G15" s="189"/>
+      <c r="H15" s="174">
         <v>3106192125</v>
       </c>
-      <c r="I15" s="180"/>
+      <c r="I15" s="175"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -5036,21 +5014,21 @@
       <c r="AA15" s="7"/>
       <c r="AB15" s="7"/>
     </row>
-    <row r="16" spans="2:28" ht="18" customHeight="1">
-      <c r="B16" s="214" t="s">
+    <row r="16" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="215"/>
-      <c r="D16" s="216"/>
-      <c r="E16" s="217" t="s">
+      <c r="C16" s="146"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="217"/>
-      <c r="G16" s="217"/>
-      <c r="H16" s="199" t="s">
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="200"/>
+      <c r="I16" s="128"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -5071,21 +5049,21 @@
       <c r="AA16" s="7"/>
       <c r="AB16" s="7"/>
     </row>
-    <row r="17" spans="2:28" ht="18" customHeight="1">
-      <c r="B17" s="220" t="s">
+    <row r="17" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="196"/>
-      <c r="D17" s="197"/>
-      <c r="E17" s="169" t="s">
+      <c r="C17" s="155"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="199" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="170"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="164" t="s">
+      <c r="F17" s="200"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="145"/>
+      <c r="I17" s="195"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -5106,21 +5084,21 @@
       <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
     </row>
-    <row r="18" spans="2:28" s="40" customFormat="1" ht="18" customHeight="1">
-      <c r="B18" s="165" t="s">
+    <row r="18" spans="2:28" s="40" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="176" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="166"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="163" t="s">
+      <c r="C18" s="177"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="172" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="163"/>
-      <c r="G18" s="163"/>
-      <c r="H18" s="163" t="s">
+      <c r="F18" s="172"/>
+      <c r="G18" s="172"/>
+      <c r="H18" s="172" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="143"/>
+      <c r="I18" s="173"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -5141,21 +5119,21 @@
       <c r="AA18" s="7"/>
       <c r="AB18" s="7"/>
     </row>
-    <row r="19" spans="2:28" s="40" customFormat="1" ht="18" customHeight="1">
-      <c r="B19" s="167">
+    <row r="19" spans="2:28" s="40" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="196">
         <v>2996897</v>
       </c>
-      <c r="C19" s="168"/>
-      <c r="D19" s="144"/>
-      <c r="E19" s="164" t="s">
+      <c r="C19" s="197"/>
+      <c r="D19" s="198"/>
+      <c r="E19" s="194" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="164"/>
-      <c r="G19" s="164"/>
-      <c r="H19" s="164" t="s">
+      <c r="F19" s="194"/>
+      <c r="G19" s="194"/>
+      <c r="H19" s="194" t="s">
         <v>30</v>
       </c>
-      <c r="I19" s="145"/>
+      <c r="I19" s="195"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -5176,371 +5154,341 @@
       <c r="AA19" s="7"/>
       <c r="AB19" s="7"/>
     </row>
-    <row r="20" spans="2:28" ht="43.5" customHeight="1">
-      <c r="B20" s="222" t="s">
+    <row r="20" spans="2:28" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="159" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="223"/>
-      <c r="D20" s="224"/>
-      <c r="E20" s="131" t="s">
+      <c r="C20" s="160"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="157" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="131"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="131" t="s">
+      <c r="F20" s="157"/>
+      <c r="G20" s="157"/>
+      <c r="H20" s="157" t="s">
         <v>33</v>
       </c>
-      <c r="I20" s="221"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="67"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67"/>
-      <c r="Q20" s="67"/>
-      <c r="R20" s="67"/>
-      <c r="S20" s="67"/>
-      <c r="T20" s="67"/>
-      <c r="U20" s="67"/>
-      <c r="V20" s="67"/>
-      <c r="W20" s="67"/>
-      <c r="X20" s="67"/>
-      <c r="Y20" s="67"/>
-      <c r="Z20" s="67"/>
-      <c r="AA20" s="67"/>
-    </row>
-    <row r="21" spans="2:28" ht="18" customHeight="1">
-      <c r="B21" s="195" t="s">
+      <c r="I20" s="158"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="66"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
+      <c r="V20" s="66"/>
+      <c r="W20" s="66"/>
+      <c r="X20" s="66"/>
+      <c r="Y20" s="66"/>
+      <c r="Z20" s="66"/>
+      <c r="AA20" s="66"/>
+    </row>
+    <row r="21" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="162" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="196"/>
-      <c r="D21" s="197"/>
-      <c r="E21" s="130" t="s">
+      <c r="C21" s="155"/>
+      <c r="D21" s="156"/>
+      <c r="E21" s="174" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="130"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="128" t="s">
+      <c r="F21" s="174"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="129"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="64"/>
-      <c r="R21" s="64"/>
-      <c r="S21" s="64"/>
-      <c r="T21" s="64"/>
-      <c r="U21" s="64"/>
-      <c r="V21" s="64"/>
-      <c r="W21" s="64"/>
-      <c r="X21" s="64"/>
-      <c r="Y21" s="64"/>
-      <c r="Z21" s="64"/>
-      <c r="AA21" s="64"/>
-    </row>
-    <row r="22" spans="2:28" ht="9.75" customHeight="1">
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
+      <c r="I21" s="207"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="63"/>
+      <c r="Q21" s="63"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="63"/>
+      <c r="T21" s="63"/>
+      <c r="U21" s="63"/>
+      <c r="V21" s="63"/>
+      <c r="W21" s="63"/>
+      <c r="X21" s="63"/>
+      <c r="Y21" s="63"/>
+      <c r="Z21" s="63"/>
+      <c r="AA21" s="63"/>
+    </row>
+    <row r="22" spans="2:28" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
-      <c r="G22" s="101"/>
-      <c r="H22" s="101"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="63"/>
-      <c r="S22" s="63"/>
-      <c r="T22" s="63"/>
-      <c r="U22" s="63"/>
-      <c r="V22" s="63"/>
-      <c r="W22" s="63"/>
-      <c r="X22" s="63"/>
-      <c r="Y22" s="63"/>
-      <c r="Z22" s="63"/>
-      <c r="AA22" s="63"/>
-    </row>
-    <row r="23" spans="2:28" ht="17.25" customHeight="1">
-      <c r="B23" s="160" t="s">
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="62"/>
+      <c r="V22" s="62"/>
+      <c r="W22" s="62"/>
+      <c r="X22" s="62"/>
+      <c r="Y22" s="62"/>
+      <c r="Z22" s="62"/>
+      <c r="AA22" s="62"/>
+    </row>
+    <row r="23" spans="2:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="201" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="161"/>
-      <c r="D23" s="161"/>
-      <c r="E23" s="161"/>
-      <c r="F23" s="161"/>
-      <c r="G23" s="161"/>
-      <c r="H23" s="161"/>
-      <c r="I23" s="162"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="63"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="63"/>
-      <c r="S23" s="63"/>
-      <c r="T23" s="63"/>
-      <c r="U23" s="63"/>
-      <c r="V23" s="63"/>
-      <c r="W23" s="63"/>
-      <c r="X23" s="63"/>
-      <c r="Y23" s="63"/>
-      <c r="Z23" s="63"/>
-      <c r="AA23" s="63"/>
-    </row>
-    <row r="24" spans="2:28" s="9" customFormat="1" ht="36.75" customHeight="1">
-      <c r="B24" s="126" t="s">
+      <c r="C23" s="202"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="202"/>
+      <c r="G23" s="202"/>
+      <c r="H23" s="202"/>
+      <c r="I23" s="203"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="62"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="62"/>
+      <c r="V23" s="62"/>
+      <c r="W23" s="62"/>
+      <c r="X23" s="62"/>
+      <c r="Y23" s="62"/>
+      <c r="Z23" s="62"/>
+      <c r="AA23" s="62"/>
+    </row>
+    <row r="24" spans="2:28" s="9" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="204" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="132" t="s">
+      <c r="C24" s="205"/>
+      <c r="D24" s="205"/>
+      <c r="E24" s="205"/>
+      <c r="F24" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="132"/>
-      <c r="H24" s="127" t="s">
+      <c r="G24" s="140"/>
+      <c r="H24" s="205" t="s">
         <v>40</v>
       </c>
-      <c r="I24" s="151"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="67"/>
-      <c r="N24" s="67"/>
-      <c r="O24" s="61"/>
-      <c r="P24" s="61"/>
-      <c r="Q24" s="61"/>
-      <c r="R24" s="61"/>
-      <c r="S24" s="61"/>
-      <c r="T24" s="61"/>
-      <c r="U24" s="61"/>
-      <c r="V24" s="61"/>
-      <c r="W24" s="67"/>
-      <c r="X24" s="67"/>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="67"/>
-      <c r="AA24" s="67"/>
+      <c r="I24" s="225"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="66"/>
+      <c r="W24" s="66"/>
+      <c r="X24" s="66"/>
+      <c r="Y24" s="66"/>
+      <c r="Z24" s="66"/>
+      <c r="AA24" s="66"/>
       <c r="AB24" s="10"/>
     </row>
-    <row r="25" spans="2:28" ht="25.5" customHeight="1">
-      <c r="B25" s="159" t="s">
+    <row r="25" spans="2:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="226" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133" t="s">
+      <c r="C25" s="208"/>
+      <c r="D25" s="208"/>
+      <c r="E25" s="208"/>
+      <c r="F25" s="208" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="133"/>
-      <c r="H25" s="159" t="s">
+      <c r="G25" s="208"/>
+      <c r="H25" s="226" t="s">
         <v>43</v>
       </c>
-      <c r="I25" s="133"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="64"/>
-      <c r="O25" s="61"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="61"/>
-      <c r="R25" s="61"/>
-      <c r="S25" s="61"/>
-      <c r="T25" s="61"/>
-      <c r="U25" s="61"/>
-      <c r="V25" s="61"/>
-      <c r="W25" s="64"/>
-      <c r="X25" s="64"/>
-      <c r="Y25" s="64"/>
-      <c r="Z25" s="64"/>
-      <c r="AA25" s="64"/>
-    </row>
-    <row r="26" spans="2:28" ht="9.9499999999999993" customHeight="1">
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
+      <c r="I25" s="208"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="W25" s="63"/>
+      <c r="X25" s="63"/>
+      <c r="Y25" s="63"/>
+      <c r="Z25" s="63"/>
+      <c r="AA25" s="63"/>
+    </row>
+    <row r="26" spans="2:28" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="63"/>
-      <c r="T26" s="63"/>
-      <c r="U26" s="63"/>
-      <c r="V26" s="63"/>
-      <c r="W26" s="63"/>
-      <c r="X26" s="63"/>
-      <c r="Y26" s="63"/>
-      <c r="Z26" s="63"/>
-      <c r="AA26" s="63"/>
-    </row>
-    <row r="27" spans="2:28" ht="18" customHeight="1">
-      <c r="B27" s="156" t="s">
+      <c r="G26" s="135"/>
+      <c r="H26" s="135"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="62"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="62"/>
+      <c r="V26" s="62"/>
+      <c r="W26" s="62"/>
+      <c r="X26" s="62"/>
+      <c r="Y26" s="62"/>
+      <c r="Z26" s="62"/>
+      <c r="AA26" s="62"/>
+    </row>
+    <row r="27" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="230" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="157"/>
-      <c r="D27" s="157"/>
-      <c r="E27" s="157"/>
-      <c r="F27" s="157"/>
-      <c r="G27" s="157"/>
-      <c r="H27" s="157"/>
-      <c r="I27" s="158"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="63"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="63"/>
-      <c r="P27" s="63"/>
-      <c r="Q27" s="63"/>
-      <c r="R27" s="63"/>
-      <c r="S27" s="63"/>
-      <c r="T27" s="63"/>
-      <c r="U27" s="63"/>
-      <c r="V27" s="63"/>
-      <c r="W27" s="63"/>
-      <c r="X27" s="63"/>
-      <c r="Y27" s="63"/>
-      <c r="Z27" s="63"/>
-      <c r="AA27" s="63"/>
-    </row>
-    <row r="28" spans="2:28" s="9" customFormat="1" ht="45.75" customHeight="1">
-      <c r="B28" s="152" t="s">
+      <c r="C27" s="231"/>
+      <c r="D27" s="231"/>
+      <c r="E27" s="231"/>
+      <c r="F27" s="231"/>
+      <c r="G27" s="231"/>
+      <c r="H27" s="231"/>
+      <c r="I27" s="232"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="62"/>
+      <c r="T27" s="62"/>
+      <c r="U27" s="62"/>
+      <c r="V27" s="62"/>
+      <c r="W27" s="62"/>
+      <c r="X27" s="62"/>
+      <c r="Y27" s="62"/>
+      <c r="Z27" s="62"/>
+      <c r="AA27" s="62"/>
+    </row>
+    <row r="28" spans="2:28" s="9" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="227" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="127"/>
-      <c r="D28" s="127"/>
-      <c r="E28" s="132" t="s">
+      <c r="C28" s="205"/>
+      <c r="D28" s="205"/>
+      <c r="E28" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="132"/>
-      <c r="G28" s="66" t="s">
+      <c r="F28" s="140"/>
+      <c r="G28" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="H28" s="127" t="s">
+      <c r="H28" s="205" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="155"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="67"/>
-      <c r="R28" s="67"/>
-      <c r="S28" s="67"/>
-      <c r="T28" s="67"/>
-      <c r="U28" s="61"/>
-      <c r="V28" s="67"/>
-      <c r="W28" s="67"/>
-      <c r="X28" s="67"/>
-      <c r="Y28" s="67"/>
-      <c r="Z28" s="67"/>
-      <c r="AA28" s="67"/>
+      <c r="I28" s="229"/>
+      <c r="J28" s="66"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="66"/>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="66"/>
+      <c r="V28" s="66"/>
+      <c r="W28" s="66"/>
+      <c r="X28" s="66"/>
+      <c r="Y28" s="66"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
       <c r="AB28" s="10"/>
     </row>
-    <row r="29" spans="2:28" ht="24" customHeight="1" thickBot="1">
-      <c r="B29" s="153" t="s">
+    <row r="29" spans="2:28" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="228" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="154"/>
-      <c r="D29" s="154"/>
-      <c r="E29" s="154" t="s">
+      <c r="C29" s="141"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="154"/>
+      <c r="F29" s="141"/>
       <c r="G29" s="43">
         <v>3124117048</v>
       </c>
-      <c r="H29" s="210" t="s">
+      <c r="H29" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="211"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="61"/>
-      <c r="L29" s="61"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="64"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="64"/>
-      <c r="R29" s="64"/>
-      <c r="S29" s="64"/>
-      <c r="T29" s="64"/>
-      <c r="U29" s="61"/>
-      <c r="V29" s="64"/>
-      <c r="W29" s="64"/>
-      <c r="X29" s="64"/>
-      <c r="Y29" s="64"/>
-      <c r="Z29" s="64"/>
-      <c r="AA29" s="64"/>
-    </row>
-    <row r="30" spans="2:28" ht="8.25" customHeight="1">
-      <c r="B30" s="63"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="63"/>
+      <c r="N29" s="63"/>
+      <c r="O29" s="63"/>
+      <c r="Q29" s="63"/>
+      <c r="R29" s="63"/>
+      <c r="S29" s="63"/>
+      <c r="T29" s="63"/>
+      <c r="V29" s="63"/>
+      <c r="W29" s="63"/>
+      <c r="X29" s="63"/>
+      <c r="Y29" s="63"/>
+      <c r="Z29" s="63"/>
+      <c r="AA29" s="63"/>
+    </row>
+    <row r="30" spans="2:28" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="62"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
-      <c r="G30" s="101"/>
-      <c r="H30" s="101"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="63"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="63"/>
-      <c r="M30" s="63"/>
-      <c r="N30" s="63"/>
-      <c r="O30" s="63"/>
-      <c r="P30" s="63"/>
-      <c r="Q30" s="63"/>
-      <c r="R30" s="63"/>
-      <c r="S30" s="63"/>
-      <c r="T30" s="63"/>
-      <c r="U30" s="63"/>
-      <c r="V30" s="63"/>
-      <c r="W30" s="63"/>
-      <c r="X30" s="63"/>
-      <c r="Y30" s="63"/>
-      <c r="Z30" s="63"/>
-      <c r="AA30" s="63"/>
-    </row>
-    <row r="31" spans="2:28" ht="18" customHeight="1">
-      <c r="B31" s="160" t="s">
+      <c r="G30" s="135"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="62"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="62"/>
+      <c r="T30" s="62"/>
+      <c r="U30" s="62"/>
+      <c r="V30" s="62"/>
+      <c r="W30" s="62"/>
+      <c r="X30" s="62"/>
+      <c r="Y30" s="62"/>
+      <c r="Z30" s="62"/>
+      <c r="AA30" s="62"/>
+    </row>
+    <row r="31" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="201" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="161"/>
-      <c r="D31" s="161"/>
-      <c r="E31" s="161"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
-      <c r="H31" s="161"/>
-      <c r="I31" s="162"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="202"/>
+      <c r="G31" s="202"/>
+      <c r="H31" s="202"/>
+      <c r="I31" s="203"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -5561,19 +5509,19 @@
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
     </row>
-    <row r="32" spans="2:28" ht="19.5" customHeight="1">
-      <c r="B32" s="212" t="s">
+    <row r="32" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="213"/>
-      <c r="G32" s="72" t="s">
+      <c r="C32" s="143"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="144"/>
+      <c r="G32" s="266" t="s">
         <v>54</v>
       </c>
-      <c r="H32" s="73"/>
-      <c r="I32" s="74"/>
+      <c r="H32" s="143"/>
+      <c r="I32" s="267"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -5594,19 +5542,19 @@
       <c r="AA32" s="7"/>
       <c r="AB32" s="7"/>
     </row>
-    <row r="33" spans="1:28" ht="30" customHeight="1">
-      <c r="B33" s="69" t="s">
+    <row r="33" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="263" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="75" t="s">
+      <c r="C33" s="264"/>
+      <c r="D33" s="264"/>
+      <c r="E33" s="264"/>
+      <c r="F33" s="265"/>
+      <c r="G33" s="268" t="s">
         <v>56</v>
       </c>
-      <c r="H33" s="70"/>
-      <c r="I33" s="76"/>
+      <c r="H33" s="264"/>
+      <c r="I33" s="269"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -5627,45 +5575,45 @@
       <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
     </row>
-    <row r="34" spans="1:28" ht="9.9499999999999993" customHeight="1">
-      <c r="B34" s="63"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="63"/>
+    <row r="34" spans="1:28" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="27"/>
       <c r="F34" s="27"/>
-      <c r="G34" s="101"/>
-      <c r="H34" s="101"/>
-      <c r="I34" s="63"/>
-      <c r="J34" s="63"/>
-      <c r="K34" s="63"/>
-      <c r="L34" s="63"/>
-      <c r="M34" s="63"/>
-      <c r="N34" s="63"/>
-      <c r="O34" s="63"/>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="63"/>
-      <c r="S34" s="63"/>
-      <c r="T34" s="63"/>
-      <c r="U34" s="63"/>
-      <c r="V34" s="63"/>
-      <c r="W34" s="63"/>
-      <c r="X34" s="63"/>
-      <c r="Y34" s="63"/>
-      <c r="Z34" s="63"/>
-      <c r="AA34" s="63"/>
-    </row>
-    <row r="35" spans="1:28" ht="18" customHeight="1">
-      <c r="B35" s="139" t="s">
+      <c r="G34" s="135"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="62"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="62"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="62"/>
+      <c r="V34" s="62"/>
+      <c r="W34" s="62"/>
+      <c r="X34" s="62"/>
+      <c r="Y34" s="62"/>
+      <c r="Z34" s="62"/>
+      <c r="AA34" s="62"/>
+    </row>
+    <row r="35" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="217" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="140"/>
-      <c r="D35" s="140"/>
-      <c r="E35" s="140"/>
-      <c r="F35" s="140"/>
-      <c r="G35" s="140"/>
-      <c r="H35" s="140"/>
-      <c r="I35" s="141"/>
+      <c r="C35" s="218"/>
+      <c r="D35" s="218"/>
+      <c r="E35" s="218"/>
+      <c r="F35" s="218"/>
+      <c r="G35" s="218"/>
+      <c r="H35" s="218"/>
+      <c r="I35" s="219"/>
       <c r="J35" s="33"/>
       <c r="K35" s="14"/>
       <c r="L35" s="14"/>
@@ -5685,23 +5633,23 @@
       <c r="Z35" s="15"/>
       <c r="AA35" s="15"/>
     </row>
-    <row r="36" spans="1:28" ht="30" customHeight="1">
+    <row r="36" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="148" t="s">
+      <c r="C36" s="222" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="149"/>
-      <c r="E36" s="149"/>
-      <c r="F36" s="150"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="224"/>
       <c r="G36" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="H36" s="146" t="s">
+      <c r="H36" s="220" t="s">
         <v>60</v>
       </c>
-      <c r="I36" s="147"/>
+      <c r="I36" s="221"/>
       <c r="J36" s="34"/>
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
@@ -5721,688 +5669,688 @@
       <c r="Z36" s="15"/>
       <c r="AA36" s="15"/>
     </row>
-    <row r="37" spans="1:28" s="11" customFormat="1" ht="14.25" customHeight="1">
-      <c r="B37" s="94" t="s">
+    <row r="37" spans="1:28" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="211" t="s">
         <v>61</v>
       </c>
-      <c r="C37" s="97"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="94" t="s">
+      <c r="C37" s="239"/>
+      <c r="D37" s="240"/>
+      <c r="E37" s="240"/>
+      <c r="F37" s="241"/>
+      <c r="G37" s="211" t="s">
         <v>62</v>
       </c>
-      <c r="H37" s="118"/>
-      <c r="I37" s="119"/>
+      <c r="H37" s="257"/>
+      <c r="I37" s="258"/>
       <c r="J37" s="33"/>
-      <c r="K37" s="67"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="64"/>
-      <c r="N37" s="64"/>
-      <c r="O37" s="64"/>
-      <c r="P37" s="64"/>
-      <c r="Q37" s="64"/>
-      <c r="R37" s="64"/>
-      <c r="S37" s="67"/>
-      <c r="T37" s="67"/>
-      <c r="U37" s="64"/>
-      <c r="V37" s="64"/>
-      <c r="W37" s="64"/>
-      <c r="X37" s="64"/>
+      <c r="K37" s="66"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="63"/>
+      <c r="O37" s="63"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="63"/>
+      <c r="R37" s="63"/>
+      <c r="S37" s="66"/>
+      <c r="T37" s="66"/>
+      <c r="U37" s="63"/>
+      <c r="V37" s="63"/>
+      <c r="W37" s="63"/>
+      <c r="X37" s="63"/>
       <c r="AB37" s="12"/>
     </row>
-    <row r="38" spans="1:28" s="11" customFormat="1" ht="14.25" customHeight="1">
-      <c r="B38" s="122"/>
-      <c r="C38" s="100"/>
-      <c r="D38" s="101"/>
-      <c r="E38" s="101"/>
-      <c r="F38" s="102"/>
-      <c r="G38" s="95"/>
-      <c r="H38" s="120"/>
-      <c r="I38" s="121"/>
+    <row r="38" spans="1:28" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="261"/>
+      <c r="C38" s="242"/>
+      <c r="D38" s="135"/>
+      <c r="E38" s="135"/>
+      <c r="F38" s="243"/>
+      <c r="G38" s="236"/>
+      <c r="H38" s="259"/>
+      <c r="I38" s="260"/>
       <c r="J38" s="33"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="64"/>
-      <c r="M38" s="64"/>
-      <c r="N38" s="64"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="64"/>
-      <c r="R38" s="64"/>
-      <c r="S38" s="67"/>
-      <c r="T38" s="67"/>
-      <c r="U38" s="64"/>
-      <c r="V38" s="64"/>
-      <c r="W38" s="64"/>
-      <c r="X38" s="64"/>
+      <c r="K38" s="66"/>
+      <c r="L38" s="63"/>
+      <c r="M38" s="63"/>
+      <c r="N38" s="63"/>
+      <c r="P38" s="63"/>
+      <c r="Q38" s="63"/>
+      <c r="R38" s="63"/>
+      <c r="S38" s="66"/>
+      <c r="T38" s="66"/>
+      <c r="U38" s="63"/>
+      <c r="V38" s="63"/>
+      <c r="W38" s="63"/>
+      <c r="X38" s="63"/>
       <c r="AB38" s="12"/>
     </row>
-    <row r="39" spans="1:28" s="11" customFormat="1" ht="14.25" customHeight="1">
-      <c r="B39" s="122"/>
-      <c r="C39" s="100"/>
-      <c r="D39" s="101"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="94" t="s">
+    <row r="39" spans="1:28" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="261"/>
+      <c r="C39" s="242"/>
+      <c r="D39" s="135"/>
+      <c r="E39" s="135"/>
+      <c r="F39" s="243"/>
+      <c r="G39" s="211" t="s">
         <v>63</v>
       </c>
-      <c r="H39" s="142" t="s">
+      <c r="H39" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="I39" s="143"/>
+      <c r="I39" s="173"/>
       <c r="J39" s="33"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="64"/>
-      <c r="M39" s="64"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="64"/>
-      <c r="P39" s="64"/>
-      <c r="Q39" s="64"/>
-      <c r="R39" s="64"/>
-      <c r="S39" s="67"/>
-      <c r="T39" s="67"/>
-      <c r="U39" s="64"/>
-      <c r="V39" s="64"/>
-      <c r="W39" s="64"/>
-      <c r="X39" s="64"/>
+      <c r="K39" s="66"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="63"/>
+      <c r="P39" s="63"/>
+      <c r="Q39" s="63"/>
+      <c r="R39" s="63"/>
+      <c r="S39" s="66"/>
+      <c r="T39" s="66"/>
+      <c r="U39" s="63"/>
+      <c r="V39" s="63"/>
+      <c r="W39" s="63"/>
+      <c r="X39" s="63"/>
       <c r="AB39" s="12"/>
     </row>
-    <row r="40" spans="1:28" s="11" customFormat="1" ht="20.25" customHeight="1">
-      <c r="B40" s="123"/>
-      <c r="C40" s="103"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="95"/>
-      <c r="H40" s="144"/>
-      <c r="I40" s="145"/>
+    <row r="40" spans="1:28" s="11" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="262"/>
+      <c r="C40" s="244"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="236"/>
+      <c r="H40" s="198"/>
+      <c r="I40" s="195"/>
       <c r="J40" s="33"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="64"/>
-      <c r="M40" s="64"/>
-      <c r="N40" s="64"/>
-      <c r="O40" s="64"/>
-      <c r="P40" s="64"/>
-      <c r="Q40" s="64"/>
-      <c r="R40" s="64"/>
-      <c r="S40" s="67"/>
-      <c r="T40" s="67"/>
-      <c r="U40" s="64"/>
-      <c r="V40" s="64"/>
-      <c r="W40" s="64"/>
-      <c r="X40" s="64"/>
+      <c r="K40" s="66"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="63"/>
+      <c r="O40" s="63"/>
+      <c r="P40" s="63"/>
+      <c r="Q40" s="63"/>
+      <c r="R40" s="63"/>
+      <c r="S40" s="66"/>
+      <c r="T40" s="66"/>
+      <c r="U40" s="63"/>
+      <c r="V40" s="63"/>
+      <c r="W40" s="63"/>
+      <c r="X40" s="63"/>
       <c r="AB40" s="12"/>
     </row>
-    <row r="41" spans="1:28" s="11" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B41" s="112" t="s">
+    <row r="41" spans="1:28" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="253" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="106"/>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
-      <c r="F41" s="108"/>
-      <c r="G41" s="94" t="s">
+      <c r="C41" s="247"/>
+      <c r="D41" s="248"/>
+      <c r="E41" s="248"/>
+      <c r="F41" s="249"/>
+      <c r="G41" s="211" t="s">
         <v>66</v>
       </c>
-      <c r="H41" s="135"/>
-      <c r="I41" s="136"/>
+      <c r="H41" s="213"/>
+      <c r="I41" s="214"/>
       <c r="J41" s="46"/>
-      <c r="K41" s="67"/>
+      <c r="K41" s="66"/>
       <c r="L41" s="59"/>
       <c r="M41" s="13"/>
       <c r="N41" s="13"/>
       <c r="O41" s="13"/>
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
-      <c r="R41" s="64"/>
+      <c r="R41" s="63"/>
       <c r="S41" s="59"/>
       <c r="T41" s="59"/>
       <c r="U41" s="13"/>
       <c r="V41" s="13"/>
       <c r="W41" s="13"/>
-      <c r="X41" s="64"/>
+      <c r="X41" s="63"/>
       <c r="Y41" s="59"/>
       <c r="Z41" s="59"/>
-      <c r="AA41" s="63"/>
+      <c r="AA41" s="62"/>
       <c r="AB41" s="12"/>
     </row>
-    <row r="42" spans="1:28" s="32" customFormat="1" ht="16.5" customHeight="1">
+    <row r="42" spans="1:28" s="32" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11"/>
-      <c r="B42" s="113"/>
-      <c r="C42" s="109"/>
-      <c r="D42" s="110"/>
-      <c r="E42" s="110"/>
-      <c r="F42" s="111"/>
-      <c r="G42" s="134"/>
-      <c r="H42" s="137"/>
-      <c r="I42" s="138"/>
+      <c r="B42" s="254"/>
+      <c r="C42" s="250"/>
+      <c r="D42" s="251"/>
+      <c r="E42" s="251"/>
+      <c r="F42" s="252"/>
+      <c r="G42" s="212"/>
+      <c r="H42" s="215"/>
+      <c r="I42" s="216"/>
       <c r="J42" s="46"/>
-      <c r="K42" s="67"/>
+      <c r="K42" s="66"/>
       <c r="L42" s="59"/>
       <c r="M42" s="13"/>
       <c r="N42" s="13"/>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
-      <c r="R42" s="64"/>
+      <c r="R42" s="63"/>
       <c r="S42" s="59"/>
       <c r="T42" s="59"/>
       <c r="U42" s="13"/>
       <c r="V42" s="13"/>
       <c r="W42" s="13"/>
-      <c r="X42" s="64"/>
+      <c r="X42" s="63"/>
       <c r="Y42" s="59"/>
       <c r="Z42" s="59"/>
-      <c r="AA42" s="63"/>
+      <c r="AA42" s="62"/>
       <c r="AB42" s="12"/>
     </row>
-    <row r="43" spans="1:28" s="32" customFormat="1" ht="13.5" customHeight="1">
+    <row r="43" spans="1:28" s="32" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
       <c r="B43" s="36"/>
-      <c r="C43" s="68"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="96"/>
-      <c r="H43" s="84"/>
-      <c r="I43" s="68"/>
+      <c r="C43" s="67"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="237"/>
+      <c r="H43" s="238"/>
+      <c r="I43" s="67"/>
       <c r="J43" s="46"/>
-      <c r="K43" s="67"/>
+      <c r="K43" s="66"/>
       <c r="L43" s="59"/>
       <c r="M43" s="13"/>
       <c r="N43" s="13"/>
       <c r="O43" s="13"/>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
-      <c r="R43" s="64"/>
+      <c r="R43" s="63"/>
       <c r="S43" s="59"/>
       <c r="T43" s="59"/>
       <c r="U43" s="13"/>
       <c r="V43" s="13"/>
       <c r="W43" s="13"/>
-      <c r="X43" s="64"/>
+      <c r="X43" s="63"/>
       <c r="Y43" s="59"/>
       <c r="Z43" s="59"/>
-      <c r="AA43" s="63"/>
+      <c r="AA43" s="62"/>
       <c r="AB43" s="12"/>
     </row>
-    <row r="44" spans="1:28" s="11" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B44" s="317" t="s">
+    <row r="44" spans="1:28" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="234" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="317"/>
-      <c r="D44" s="317"/>
-      <c r="E44" s="317"/>
-      <c r="F44" s="317"/>
-      <c r="G44" s="317"/>
-      <c r="H44" s="317"/>
-      <c r="I44" s="318"/>
-      <c r="J44" s="67"/>
-      <c r="K44" s="67"/>
+      <c r="C44" s="234"/>
+      <c r="D44" s="234"/>
+      <c r="E44" s="234"/>
+      <c r="F44" s="234"/>
+      <c r="G44" s="234"/>
+      <c r="H44" s="234"/>
+      <c r="I44" s="235"/>
+      <c r="J44" s="66"/>
+      <c r="K44" s="66"/>
       <c r="L44" s="59"/>
       <c r="M44" s="13"/>
       <c r="N44" s="13"/>
       <c r="O44" s="13"/>
       <c r="P44" s="13"/>
       <c r="Q44" s="13"/>
-      <c r="R44" s="64"/>
+      <c r="R44" s="63"/>
       <c r="S44" s="59"/>
       <c r="T44" s="59"/>
       <c r="U44" s="13"/>
       <c r="V44" s="13"/>
       <c r="W44" s="13"/>
-      <c r="X44" s="64"/>
+      <c r="X44" s="63"/>
       <c r="Y44" s="59"/>
       <c r="Z44" s="59"/>
-      <c r="AA44" s="63"/>
+      <c r="AA44" s="62"/>
       <c r="AB44" s="12"/>
     </row>
-    <row r="45" spans="1:28" ht="68.25" customHeight="1">
-      <c r="B45" s="299" t="s">
+    <row r="45" spans="1:28" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="152" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="202"/>
-      <c r="D45" s="201" t="s">
+      <c r="C45" s="130"/>
+      <c r="D45" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="E45" s="202"/>
-      <c r="F45" s="300" t="s">
+      <c r="E45" s="130"/>
+      <c r="F45" s="133" t="s">
         <v>70</v>
       </c>
-      <c r="G45" s="300" t="s">
+      <c r="G45" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="H45" s="218" t="s">
+      <c r="H45" s="149" t="s">
         <v>72</v>
       </c>
-      <c r="I45" s="301" t="s">
+      <c r="I45" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="J45" s="67"/>
-      <c r="K45" s="67"/>
-      <c r="L45" s="67"/>
-      <c r="M45" s="67"/>
-      <c r="N45" s="67"/>
-      <c r="O45" s="67"/>
-      <c r="P45" s="67"/>
-      <c r="Q45" s="67"/>
-      <c r="R45" s="67"/>
-      <c r="S45" s="67"/>
-      <c r="T45" s="67"/>
-      <c r="U45" s="67"/>
-      <c r="V45" s="67"/>
-      <c r="W45" s="67"/>
-      <c r="X45" s="67"/>
-      <c r="Y45" s="67"/>
-      <c r="Z45" s="67"/>
-      <c r="AA45" s="67"/>
-    </row>
-    <row r="46" spans="1:28" ht="24" customHeight="1">
-      <c r="B46" s="302"/>
-      <c r="C46" s="204"/>
-      <c r="D46" s="203"/>
-      <c r="E46" s="204"/>
-      <c r="F46" s="206"/>
-      <c r="G46" s="205"/>
-      <c r="H46" s="219"/>
-      <c r="I46" s="303"/>
-      <c r="J46" s="67"/>
-      <c r="K46" s="67"/>
-      <c r="L46" s="67"/>
-      <c r="M46" s="67"/>
-      <c r="N46" s="67"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="67"/>
-      <c r="Q46" s="67"/>
-      <c r="R46" s="67"/>
-      <c r="S46" s="67"/>
-      <c r="T46" s="67"/>
-      <c r="U46" s="67"/>
-      <c r="V46" s="67"/>
-      <c r="W46" s="67"/>
-      <c r="X46" s="67"/>
-      <c r="Y46" s="67"/>
-      <c r="Z46" s="67"/>
-      <c r="AA46" s="67"/>
-    </row>
-    <row r="47" spans="1:28" ht="53.45" customHeight="1">
-      <c r="B47" s="304" t="s">
+      <c r="J45" s="66"/>
+      <c r="K45" s="66"/>
+      <c r="L45" s="66"/>
+      <c r="M45" s="66"/>
+      <c r="N45" s="66"/>
+      <c r="O45" s="66"/>
+      <c r="P45" s="66"/>
+      <c r="Q45" s="66"/>
+      <c r="R45" s="66"/>
+      <c r="S45" s="66"/>
+      <c r="T45" s="66"/>
+      <c r="U45" s="66"/>
+      <c r="V45" s="66"/>
+      <c r="W45" s="66"/>
+      <c r="X45" s="66"/>
+      <c r="Y45" s="66"/>
+      <c r="Z45" s="66"/>
+      <c r="AA45" s="66"/>
+    </row>
+    <row r="46" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="153"/>
+      <c r="C46" s="132"/>
+      <c r="D46" s="131"/>
+      <c r="E46" s="132"/>
+      <c r="F46" s="134"/>
+      <c r="G46" s="151"/>
+      <c r="H46" s="150"/>
+      <c r="I46" s="210"/>
+      <c r="J46" s="66"/>
+      <c r="K46" s="66"/>
+      <c r="L46" s="66"/>
+      <c r="M46" s="66"/>
+      <c r="N46" s="66"/>
+      <c r="O46" s="66"/>
+      <c r="P46" s="66"/>
+      <c r="Q46" s="66"/>
+      <c r="R46" s="66"/>
+      <c r="S46" s="66"/>
+      <c r="T46" s="66"/>
+      <c r="U46" s="66"/>
+      <c r="V46" s="66"/>
+      <c r="W46" s="66"/>
+      <c r="X46" s="66"/>
+      <c r="Y46" s="66"/>
+      <c r="Z46" s="66"/>
+      <c r="AA46" s="66"/>
+    </row>
+    <row r="47" spans="1:28" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="117" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="92"/>
-      <c r="D47" s="225" t="s">
+      <c r="C47" s="118"/>
+      <c r="D47" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="E47" s="226"/>
-      <c r="F47" s="286">
+      <c r="E47" s="82"/>
+      <c r="F47" s="119">
         <v>46182</v>
       </c>
-      <c r="G47" s="284">
+      <c r="G47" s="121">
         <v>46189</v>
       </c>
-      <c r="H47" s="117" t="s">
+      <c r="H47" s="123" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="305" t="s">
+      <c r="I47" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="J47" s="64"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="67"/>
-      <c r="M47" s="67"/>
-      <c r="N47" s="67"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
-      <c r="R47" s="67"/>
-      <c r="S47" s="67"/>
-      <c r="T47" s="67"/>
-      <c r="U47" s="67"/>
-      <c r="V47" s="67"/>
-      <c r="W47" s="67"/>
-      <c r="X47" s="67"/>
-      <c r="Y47" s="67"/>
-      <c r="Z47" s="67"/>
-      <c r="AA47" s="67"/>
-    </row>
-    <row r="48" spans="1:28" ht="63.75" customHeight="1">
-      <c r="B48" s="304"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="227"/>
-      <c r="E48" s="228"/>
-      <c r="F48" s="287"/>
-      <c r="G48" s="285"/>
-      <c r="H48" s="117"/>
-      <c r="I48" s="306"/>
-      <c r="J48" s="64"/>
-      <c r="K48" s="67"/>
-      <c r="L48" s="67"/>
-      <c r="M48" s="67"/>
-      <c r="N48" s="67"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="67"/>
-      <c r="Q48" s="67"/>
-      <c r="R48" s="67"/>
-      <c r="S48" s="67"/>
-      <c r="T48" s="67"/>
-      <c r="U48" s="67"/>
-      <c r="V48" s="67"/>
-      <c r="W48" s="67"/>
-      <c r="X48" s="67"/>
-      <c r="Y48" s="67"/>
-      <c r="Z48" s="67"/>
-      <c r="AA48" s="67"/>
-    </row>
-    <row r="49" spans="2:28" ht="32.1" customHeight="1">
-      <c r="B49" s="304" t="s">
+      <c r="J47" s="63"/>
+      <c r="K47" s="66"/>
+      <c r="L47" s="66"/>
+      <c r="M47" s="66"/>
+      <c r="N47" s="66"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="66"/>
+      <c r="S47" s="66"/>
+      <c r="T47" s="66"/>
+      <c r="U47" s="66"/>
+      <c r="V47" s="66"/>
+      <c r="W47" s="66"/>
+      <c r="X47" s="66"/>
+      <c r="Y47" s="66"/>
+      <c r="Z47" s="66"/>
+      <c r="AA47" s="66"/>
+    </row>
+    <row r="48" spans="1:28" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="117"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="120"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="123"/>
+      <c r="I48" s="79"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="66"/>
+      <c r="L48" s="66"/>
+      <c r="M48" s="66"/>
+      <c r="N48" s="66"/>
+      <c r="O48" s="66"/>
+      <c r="P48" s="66"/>
+      <c r="Q48" s="66"/>
+      <c r="R48" s="66"/>
+      <c r="S48" s="66"/>
+      <c r="T48" s="66"/>
+      <c r="U48" s="66"/>
+      <c r="V48" s="66"/>
+      <c r="W48" s="66"/>
+      <c r="X48" s="66"/>
+      <c r="Y48" s="66"/>
+      <c r="Z48" s="66"/>
+      <c r="AA48" s="66"/>
+    </row>
+    <row r="49" spans="2:28" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="117" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="92"/>
-      <c r="D49" s="92" t="s">
+      <c r="C49" s="118"/>
+      <c r="D49" s="118" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="92"/>
-      <c r="F49" s="114">
+      <c r="E49" s="118"/>
+      <c r="F49" s="124">
         <v>46189</v>
       </c>
-      <c r="G49" s="116">
+      <c r="G49" s="126">
         <v>46196</v>
       </c>
-      <c r="H49" s="117" t="s">
+      <c r="H49" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="I49" s="307" t="s">
+      <c r="I49" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="64"/>
-      <c r="K49" s="67"/>
-      <c r="L49" s="67"/>
-      <c r="M49" s="67"/>
-      <c r="N49" s="67"/>
-      <c r="O49" s="67"/>
-      <c r="P49" s="67"/>
-      <c r="Q49" s="67"/>
-      <c r="R49" s="67"/>
-      <c r="S49" s="67"/>
-      <c r="T49" s="67"/>
-      <c r="U49" s="67"/>
-      <c r="V49" s="67"/>
-      <c r="W49" s="67"/>
-      <c r="X49" s="67"/>
-      <c r="Y49" s="67"/>
-      <c r="Z49" s="67"/>
-      <c r="AA49" s="67"/>
-    </row>
-    <row r="50" spans="2:28" ht="74.25" customHeight="1">
-      <c r="B50" s="304"/>
-      <c r="C50" s="92"/>
-      <c r="D50" s="92"/>
-      <c r="E50" s="92"/>
-      <c r="F50" s="115"/>
-      <c r="G50" s="117"/>
-      <c r="H50" s="117"/>
-      <c r="I50" s="307"/>
-      <c r="J50" s="64"/>
-      <c r="K50" s="67"/>
-      <c r="L50" s="67"/>
-      <c r="M50" s="67"/>
-      <c r="N50" s="67"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="67"/>
-      <c r="Q50" s="67"/>
-      <c r="R50" s="67"/>
-      <c r="S50" s="67"/>
-      <c r="T50" s="67"/>
-      <c r="U50" s="67"/>
-      <c r="V50" s="67"/>
-      <c r="W50" s="67"/>
-      <c r="X50" s="67"/>
-      <c r="Y50" s="67"/>
-      <c r="Z50" s="67"/>
-      <c r="AA50" s="67"/>
-    </row>
-    <row r="51" spans="2:28" ht="18.75" customHeight="1">
-      <c r="B51" s="304" t="s">
+      <c r="J49" s="63"/>
+      <c r="K49" s="66"/>
+      <c r="L49" s="66"/>
+      <c r="M49" s="66"/>
+      <c r="N49" s="66"/>
+      <c r="O49" s="66"/>
+      <c r="P49" s="66"/>
+      <c r="Q49" s="66"/>
+      <c r="R49" s="66"/>
+      <c r="S49" s="66"/>
+      <c r="T49" s="66"/>
+      <c r="U49" s="66"/>
+      <c r="V49" s="66"/>
+      <c r="W49" s="66"/>
+      <c r="X49" s="66"/>
+      <c r="Y49" s="66"/>
+      <c r="Z49" s="66"/>
+      <c r="AA49" s="66"/>
+    </row>
+    <row r="50" spans="2:28" ht="74.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="117"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="125"/>
+      <c r="G50" s="123"/>
+      <c r="H50" s="123"/>
+      <c r="I50" s="80"/>
+      <c r="J50" s="63"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="66"/>
+      <c r="M50" s="66"/>
+      <c r="N50" s="66"/>
+      <c r="O50" s="66"/>
+      <c r="P50" s="66"/>
+      <c r="Q50" s="66"/>
+      <c r="R50" s="66"/>
+      <c r="S50" s="66"/>
+      <c r="T50" s="66"/>
+      <c r="U50" s="66"/>
+      <c r="V50" s="66"/>
+      <c r="W50" s="66"/>
+      <c r="X50" s="66"/>
+      <c r="Y50" s="66"/>
+      <c r="Z50" s="66"/>
+      <c r="AA50" s="66"/>
+    </row>
+    <row r="51" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="C51" s="92"/>
-      <c r="D51" s="92" t="s">
+      <c r="C51" s="118"/>
+      <c r="D51" s="118" t="s">
         <v>83</v>
       </c>
-      <c r="E51" s="92"/>
-      <c r="F51" s="114">
+      <c r="E51" s="118"/>
+      <c r="F51" s="124">
         <v>46196</v>
       </c>
-      <c r="G51" s="116">
+      <c r="G51" s="126">
         <v>46203</v>
       </c>
-      <c r="H51" s="117" t="s">
+      <c r="H51" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="I51" s="307" t="s">
+      <c r="I51" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="J51" s="64"/>
-      <c r="K51" s="67"/>
-      <c r="L51" s="67"/>
-      <c r="M51" s="67"/>
-      <c r="N51" s="67"/>
-      <c r="O51" s="67"/>
-      <c r="P51" s="67"/>
-      <c r="Q51" s="67"/>
-      <c r="R51" s="67"/>
-      <c r="S51" s="67"/>
-      <c r="T51" s="67"/>
-      <c r="U51" s="67"/>
-      <c r="V51" s="67"/>
-      <c r="W51" s="67"/>
-      <c r="X51" s="67"/>
-      <c r="Y51" s="67"/>
-      <c r="Z51" s="67"/>
-      <c r="AA51" s="67"/>
-    </row>
-    <row r="52" spans="2:28" ht="87.75" customHeight="1">
-      <c r="B52" s="304"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="92"/>
-      <c r="E52" s="92"/>
-      <c r="F52" s="115"/>
-      <c r="G52" s="117"/>
-      <c r="H52" s="117"/>
-      <c r="I52" s="307"/>
-      <c r="J52" s="64"/>
-      <c r="K52" s="67"/>
-      <c r="L52" s="67"/>
-      <c r="M52" s="67"/>
-      <c r="N52" s="67"/>
-      <c r="O52" s="67"/>
-      <c r="P52" s="67"/>
-      <c r="Q52" s="67"/>
-      <c r="R52" s="67"/>
-      <c r="S52" s="67"/>
-      <c r="T52" s="67"/>
-      <c r="U52" s="67"/>
-      <c r="V52" s="67"/>
-      <c r="W52" s="67"/>
-      <c r="X52" s="67"/>
-      <c r="Y52" s="67"/>
-      <c r="Z52" s="67"/>
-      <c r="AA52" s="67"/>
-    </row>
-    <row r="53" spans="2:28" ht="18.75" customHeight="1">
-      <c r="B53" s="304" t="s">
+      <c r="J51" s="63"/>
+      <c r="K51" s="66"/>
+      <c r="L51" s="66"/>
+      <c r="M51" s="66"/>
+      <c r="N51" s="66"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="66"/>
+      <c r="S51" s="66"/>
+      <c r="T51" s="66"/>
+      <c r="U51" s="66"/>
+      <c r="V51" s="66"/>
+      <c r="W51" s="66"/>
+      <c r="X51" s="66"/>
+      <c r="Y51" s="66"/>
+      <c r="Z51" s="66"/>
+      <c r="AA51" s="66"/>
+    </row>
+    <row r="52" spans="2:28" ht="87.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="117"/>
+      <c r="C52" s="118"/>
+      <c r="D52" s="118"/>
+      <c r="E52" s="118"/>
+      <c r="F52" s="125"/>
+      <c r="G52" s="123"/>
+      <c r="H52" s="123"/>
+      <c r="I52" s="80"/>
+      <c r="J52" s="63"/>
+      <c r="K52" s="66"/>
+      <c r="L52" s="66"/>
+      <c r="M52" s="66"/>
+      <c r="N52" s="66"/>
+      <c r="O52" s="66"/>
+      <c r="P52" s="66"/>
+      <c r="Q52" s="66"/>
+      <c r="R52" s="66"/>
+      <c r="S52" s="66"/>
+      <c r="T52" s="66"/>
+      <c r="U52" s="66"/>
+      <c r="V52" s="66"/>
+      <c r="W52" s="66"/>
+      <c r="X52" s="66"/>
+      <c r="Y52" s="66"/>
+      <c r="Z52" s="66"/>
+      <c r="AA52" s="66"/>
+    </row>
+    <row r="53" spans="2:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="92"/>
-      <c r="D53" s="92" t="s">
+      <c r="C53" s="118"/>
+      <c r="D53" s="118" t="s">
         <v>83</v>
       </c>
-      <c r="E53" s="92"/>
-      <c r="F53" s="114">
+      <c r="E53" s="118"/>
+      <c r="F53" s="124">
         <v>46203</v>
       </c>
-      <c r="G53" s="116">
+      <c r="G53" s="126">
         <v>46210</v>
       </c>
-      <c r="H53" s="117" t="s">
+      <c r="H53" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="I53" s="306" t="s">
+      <c r="I53" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="J53" s="64"/>
-      <c r="K53" s="67"/>
-      <c r="L53" s="67"/>
-      <c r="M53" s="67"/>
-      <c r="N53" s="67"/>
-      <c r="O53" s="67"/>
-      <c r="P53" s="67"/>
-      <c r="Q53" s="67"/>
-      <c r="R53" s="67"/>
-      <c r="S53" s="67"/>
-      <c r="T53" s="67"/>
-      <c r="U53" s="67"/>
-      <c r="V53" s="67"/>
-      <c r="W53" s="67"/>
-      <c r="X53" s="67"/>
-      <c r="Y53" s="67"/>
-      <c r="Z53" s="67"/>
-      <c r="AA53" s="67"/>
-    </row>
-    <row r="54" spans="2:28" ht="95.25" customHeight="1">
-      <c r="B54" s="308"/>
-      <c r="C54" s="297"/>
-      <c r="D54" s="297"/>
-      <c r="E54" s="297"/>
-      <c r="F54" s="298"/>
-      <c r="G54" s="289"/>
-      <c r="H54" s="289"/>
-      <c r="I54" s="306"/>
-      <c r="J54" s="64"/>
-      <c r="K54" s="67"/>
-      <c r="L54" s="67"/>
-      <c r="M54" s="67"/>
-      <c r="N54" s="67"/>
-      <c r="O54" s="67"/>
-      <c r="P54" s="67"/>
-      <c r="Q54" s="67"/>
-      <c r="R54" s="67"/>
-      <c r="S54" s="67"/>
-      <c r="T54" s="67"/>
-      <c r="U54" s="67"/>
-      <c r="V54" s="67"/>
-      <c r="W54" s="67"/>
-      <c r="X54" s="67"/>
-      <c r="Y54" s="67"/>
-      <c r="Z54" s="67"/>
-      <c r="AA54" s="67"/>
-    </row>
-    <row r="55" spans="2:28" ht="15" customHeight="1">
-      <c r="B55" s="309" t="s">
+      <c r="J53" s="63"/>
+      <c r="K53" s="66"/>
+      <c r="L53" s="66"/>
+      <c r="M53" s="66"/>
+      <c r="N53" s="66"/>
+      <c r="O53" s="66"/>
+      <c r="P53" s="66"/>
+      <c r="Q53" s="66"/>
+      <c r="R53" s="66"/>
+      <c r="S53" s="66"/>
+      <c r="T53" s="66"/>
+      <c r="U53" s="66"/>
+      <c r="V53" s="66"/>
+      <c r="W53" s="66"/>
+      <c r="X53" s="66"/>
+      <c r="Y53" s="66"/>
+      <c r="Z53" s="66"/>
+      <c r="AA53" s="66"/>
+    </row>
+    <row r="54" spans="2:28" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="136"/>
+      <c r="C54" s="137"/>
+      <c r="D54" s="137"/>
+      <c r="E54" s="137"/>
+      <c r="F54" s="255"/>
+      <c r="G54" s="256"/>
+      <c r="H54" s="256"/>
+      <c r="I54" s="79"/>
+      <c r="J54" s="63"/>
+      <c r="K54" s="66"/>
+      <c r="L54" s="66"/>
+      <c r="M54" s="66"/>
+      <c r="N54" s="66"/>
+      <c r="O54" s="66"/>
+      <c r="P54" s="66"/>
+      <c r="Q54" s="66"/>
+      <c r="R54" s="66"/>
+      <c r="S54" s="66"/>
+      <c r="T54" s="66"/>
+      <c r="U54" s="66"/>
+      <c r="V54" s="66"/>
+      <c r="W54" s="66"/>
+      <c r="X54" s="66"/>
+      <c r="Y54" s="66"/>
+      <c r="Z54" s="66"/>
+      <c r="AA54" s="66"/>
+    </row>
+    <row r="55" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="C55" s="293"/>
-      <c r="D55" s="293" t="s">
+      <c r="C55" s="114"/>
+      <c r="D55" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="E55" s="293"/>
-      <c r="F55" s="294">
+      <c r="E55" s="114"/>
+      <c r="F55" s="70">
         <v>46203</v>
       </c>
-      <c r="G55" s="295">
+      <c r="G55" s="72">
         <v>46210</v>
       </c>
-      <c r="H55" s="296" t="s">
+      <c r="H55" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="I55" s="310" t="s">
+      <c r="I55" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="J55" s="64"/>
-      <c r="K55" s="67"/>
-      <c r="L55" s="67"/>
-      <c r="M55" s="67"/>
-      <c r="N55" s="67"/>
-      <c r="O55" s="67"/>
-      <c r="P55" s="67"/>
-      <c r="Q55" s="67"/>
-      <c r="R55" s="67"/>
-      <c r="S55" s="67"/>
-      <c r="T55" s="67"/>
-      <c r="U55" s="67"/>
-      <c r="V55" s="67"/>
-      <c r="W55" s="67"/>
-      <c r="X55" s="67"/>
-      <c r="Y55" s="67"/>
-      <c r="Z55" s="67"/>
-      <c r="AA55" s="67"/>
-    </row>
-    <row r="56" spans="2:28" ht="44.25" customHeight="1">
-      <c r="B56" s="311"/>
-      <c r="C56" s="312"/>
-      <c r="D56" s="312"/>
-      <c r="E56" s="312"/>
-      <c r="F56" s="313"/>
-      <c r="G56" s="314"/>
-      <c r="H56" s="315"/>
-      <c r="I56" s="316"/>
-      <c r="J56" s="64"/>
-      <c r="K56" s="67"/>
-      <c r="L56" s="67"/>
-      <c r="M56" s="67"/>
-      <c r="N56" s="67"/>
-      <c r="O56" s="67"/>
-      <c r="P56" s="67"/>
-      <c r="Q56" s="67"/>
-      <c r="R56" s="67"/>
-      <c r="S56" s="67"/>
-      <c r="T56" s="67"/>
-      <c r="U56" s="67"/>
-      <c r="V56" s="67"/>
-      <c r="W56" s="67"/>
-      <c r="X56" s="67"/>
-      <c r="Y56" s="67"/>
-      <c r="Z56" s="67"/>
-      <c r="AA56" s="67"/>
-    </row>
-    <row r="57" spans="2:28" ht="15" customHeight="1">
-      <c r="B57" s="290"/>
-      <c r="C57" s="290"/>
-      <c r="D57" s="290"/>
-      <c r="E57" s="290"/>
-      <c r="F57" s="290"/>
-      <c r="G57" s="290"/>
-      <c r="H57" s="290"/>
-      <c r="I57" s="288"/>
-      <c r="J57" s="64"/>
-      <c r="K57" s="67"/>
-      <c r="L57" s="67"/>
-      <c r="M57" s="67"/>
-      <c r="N57" s="67"/>
-      <c r="O57" s="67"/>
-      <c r="P57" s="67"/>
-      <c r="Q57" s="67"/>
-      <c r="R57" s="67"/>
-      <c r="S57" s="67"/>
-      <c r="T57" s="67"/>
-      <c r="U57" s="67"/>
-      <c r="V57" s="67"/>
-      <c r="W57" s="67"/>
-      <c r="X57" s="67"/>
-      <c r="Y57" s="67"/>
-      <c r="Z57" s="67"/>
-      <c r="AA57" s="67"/>
-    </row>
-    <row r="58" spans="2:28" ht="23.25" customHeight="1">
-      <c r="B58" s="291" t="s">
+      <c r="J55" s="63"/>
+      <c r="K55" s="66"/>
+      <c r="L55" s="66"/>
+      <c r="M55" s="66"/>
+      <c r="N55" s="66"/>
+      <c r="O55" s="66"/>
+      <c r="P55" s="66"/>
+      <c r="Q55" s="66"/>
+      <c r="R55" s="66"/>
+      <c r="S55" s="66"/>
+      <c r="T55" s="66"/>
+      <c r="U55" s="66"/>
+      <c r="V55" s="66"/>
+      <c r="W55" s="66"/>
+      <c r="X55" s="66"/>
+      <c r="Y55" s="66"/>
+      <c r="Z55" s="66"/>
+      <c r="AA55" s="66"/>
+    </row>
+    <row r="56" spans="2:28" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="115"/>
+      <c r="C56" s="116"/>
+      <c r="D56" s="116"/>
+      <c r="E56" s="116"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="75"/>
+      <c r="I56" s="77"/>
+      <c r="J56" s="63"/>
+      <c r="K56" s="66"/>
+      <c r="L56" s="66"/>
+      <c r="M56" s="66"/>
+      <c r="N56" s="66"/>
+      <c r="O56" s="66"/>
+      <c r="P56" s="66"/>
+      <c r="Q56" s="66"/>
+      <c r="R56" s="66"/>
+      <c r="S56" s="66"/>
+      <c r="T56" s="66"/>
+      <c r="U56" s="66"/>
+      <c r="V56" s="66"/>
+      <c r="W56" s="66"/>
+      <c r="X56" s="66"/>
+      <c r="Y56" s="66"/>
+      <c r="Z56" s="66"/>
+      <c r="AA56" s="66"/>
+    </row>
+    <row r="57" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="69"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="69"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="69"/>
+      <c r="H57" s="69"/>
+      <c r="I57" s="68"/>
+      <c r="J57" s="63"/>
+      <c r="K57" s="66"/>
+      <c r="L57" s="66"/>
+      <c r="M57" s="66"/>
+      <c r="N57" s="66"/>
+      <c r="O57" s="66"/>
+      <c r="P57" s="66"/>
+      <c r="Q57" s="66"/>
+      <c r="R57" s="66"/>
+      <c r="S57" s="66"/>
+      <c r="T57" s="66"/>
+      <c r="U57" s="66"/>
+      <c r="V57" s="66"/>
+      <c r="W57" s="66"/>
+      <c r="X57" s="66"/>
+      <c r="Y57" s="66"/>
+      <c r="Z57" s="66"/>
+      <c r="AA57" s="66"/>
+    </row>
+    <row r="58" spans="2:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="270" t="s">
         <v>92</v>
       </c>
-      <c r="C58" s="292"/>
-      <c r="D58" s="292"/>
-      <c r="E58" s="292"/>
-      <c r="F58" s="292"/>
-      <c r="G58" s="292"/>
-      <c r="H58" s="292"/>
-      <c r="I58" s="78"/>
+      <c r="C58" s="271"/>
+      <c r="D58" s="271"/>
+      <c r="E58" s="271"/>
+      <c r="F58" s="271"/>
+      <c r="G58" s="271"/>
+      <c r="H58" s="271"/>
+      <c r="I58" s="272"/>
       <c r="J58" s="14"/>
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
@@ -6422,17 +6370,17 @@
       <c r="Z58" s="14"/>
       <c r="AA58" s="14"/>
     </row>
-    <row r="59" spans="2:28" ht="19.5" customHeight="1">
-      <c r="B59" s="207" t="s">
+    <row r="59" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="C59" s="208"/>
-      <c r="D59" s="208"/>
-      <c r="E59" s="208"/>
-      <c r="F59" s="208"/>
-      <c r="G59" s="208"/>
-      <c r="H59" s="208"/>
-      <c r="I59" s="209"/>
+      <c r="C59" s="93"/>
+      <c r="D59" s="93"/>
+      <c r="E59" s="93"/>
+      <c r="F59" s="93"/>
+      <c r="G59" s="93"/>
+      <c r="H59" s="93"/>
+      <c r="I59" s="94"/>
       <c r="J59" s="14"/>
       <c r="K59" s="14"/>
       <c r="L59" s="14"/>
@@ -6452,17 +6400,17 @@
       <c r="Z59" s="14"/>
       <c r="AA59" s="14"/>
     </row>
-    <row r="60" spans="2:28" ht="11.25" customHeight="1">
-      <c r="B60" s="237" t="s">
+    <row r="60" spans="2:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="C60" s="238"/>
-      <c r="D60" s="238"/>
-      <c r="E60" s="238"/>
-      <c r="F60" s="238"/>
-      <c r="G60" s="238"/>
-      <c r="H60" s="238"/>
-      <c r="I60" s="239"/>
+      <c r="C60" s="97"/>
+      <c r="D60" s="97"/>
+      <c r="E60" s="97"/>
+      <c r="F60" s="97"/>
+      <c r="G60" s="97"/>
+      <c r="H60" s="97"/>
+      <c r="I60" s="98"/>
       <c r="J60" s="16"/>
       <c r="K60" s="16"/>
       <c r="L60" s="16"/>
@@ -6482,15 +6430,15 @@
       <c r="Z60" s="16"/>
       <c r="AA60" s="16"/>
     </row>
-    <row r="61" spans="2:28" ht="11.25" customHeight="1">
-      <c r="B61" s="240"/>
-      <c r="C61" s="241"/>
-      <c r="D61" s="241"/>
-      <c r="E61" s="241"/>
-      <c r="F61" s="241"/>
-      <c r="G61" s="241"/>
-      <c r="H61" s="241"/>
-      <c r="I61" s="242"/>
+    <row r="61" spans="2:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="99"/>
+      <c r="C61" s="100"/>
+      <c r="D61" s="100"/>
+      <c r="E61" s="100"/>
+      <c r="F61" s="100"/>
+      <c r="G61" s="100"/>
+      <c r="H61" s="100"/>
+      <c r="I61" s="101"/>
       <c r="J61" s="16"/>
       <c r="K61" s="16"/>
       <c r="L61" s="16"/>
@@ -6510,17 +6458,17 @@
       <c r="Z61" s="16"/>
       <c r="AA61" s="16"/>
     </row>
-    <row r="62" spans="2:28" s="39" customFormat="1" ht="18" customHeight="1">
-      <c r="B62" s="240" t="s">
+    <row r="62" spans="2:28" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="C62" s="241"/>
-      <c r="D62" s="241"/>
-      <c r="E62" s="241"/>
-      <c r="F62" s="241"/>
-      <c r="G62" s="241"/>
-      <c r="H62" s="241"/>
-      <c r="I62" s="242"/>
+      <c r="C62" s="100"/>
+      <c r="D62" s="100"/>
+      <c r="E62" s="100"/>
+      <c r="F62" s="100"/>
+      <c r="G62" s="100"/>
+      <c r="H62" s="100"/>
+      <c r="I62" s="101"/>
       <c r="J62" s="37"/>
       <c r="K62" s="37"/>
       <c r="L62" s="37"/>
@@ -6541,17 +6489,17 @@
       <c r="AA62" s="37"/>
       <c r="AB62" s="38"/>
     </row>
-    <row r="63" spans="2:28" ht="18" customHeight="1" thickBot="1">
-      <c r="B63" s="243" t="s">
+    <row r="63" spans="2:28" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="104" t="s">
         <v>96</v>
       </c>
-      <c r="C63" s="244"/>
-      <c r="D63" s="244"/>
-      <c r="E63" s="244"/>
-      <c r="F63" s="244"/>
-      <c r="G63" s="244"/>
-      <c r="H63" s="244"/>
-      <c r="I63" s="245"/>
+      <c r="C63" s="105"/>
+      <c r="D63" s="105"/>
+      <c r="E63" s="105"/>
+      <c r="F63" s="105"/>
+      <c r="G63" s="105"/>
+      <c r="H63" s="105"/>
+      <c r="I63" s="106"/>
       <c r="J63" s="16"/>
       <c r="K63" s="16"/>
       <c r="L63" s="16"/>
@@ -6571,352 +6519,348 @@
       <c r="Z63" s="16"/>
       <c r="AA63" s="16"/>
     </row>
-    <row r="64" spans="2:28" ht="45" customHeight="1">
+    <row r="64" spans="2:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="C64" s="124" t="s">
+      <c r="C64" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="D64" s="124"/>
-      <c r="E64" s="124" t="s">
+      <c r="D64" s="102"/>
+      <c r="E64" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="F64" s="124"/>
-      <c r="G64" s="88" t="s">
+      <c r="F64" s="102"/>
+      <c r="G64" s="280" t="s">
         <v>100</v>
       </c>
-      <c r="H64" s="124" t="s">
+      <c r="H64" s="102" t="s">
         <v>101</v>
       </c>
-      <c r="I64" s="90" t="s">
+      <c r="I64" s="282" t="s">
         <v>102</v>
       </c>
-      <c r="J64" s="67"/>
-      <c r="K64" s="67"/>
-      <c r="L64" s="67"/>
-      <c r="M64" s="67"/>
-      <c r="N64" s="67"/>
-      <c r="O64" s="67"/>
-      <c r="P64" s="67"/>
-      <c r="Q64" s="67"/>
-      <c r="R64" s="67"/>
-      <c r="S64" s="67"/>
-      <c r="T64" s="67"/>
-      <c r="U64" s="67"/>
-      <c r="V64" s="67"/>
-      <c r="W64" s="67"/>
-      <c r="X64" s="67"/>
-      <c r="Y64" s="67"/>
-      <c r="Z64" s="67"/>
-      <c r="AA64" s="67"/>
-      <c r="AB64" s="67"/>
-    </row>
-    <row r="65" spans="2:28" ht="32.25" customHeight="1" thickBot="1">
+      <c r="J64" s="66"/>
+      <c r="K64" s="66"/>
+      <c r="L64" s="66"/>
+      <c r="M64" s="66"/>
+      <c r="N64" s="66"/>
+      <c r="O64" s="66"/>
+      <c r="P64" s="66"/>
+      <c r="Q64" s="66"/>
+      <c r="R64" s="66"/>
+      <c r="S64" s="66"/>
+      <c r="T64" s="66"/>
+      <c r="U64" s="66"/>
+      <c r="V64" s="66"/>
+      <c r="W64" s="66"/>
+      <c r="X64" s="66"/>
+      <c r="Y64" s="66"/>
+      <c r="Z64" s="66"/>
+      <c r="AA64" s="66"/>
+      <c r="AB64" s="66"/>
+    </row>
+    <row r="65" spans="2:28" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="247">
+      <c r="C65" s="109">
         <v>2</v>
       </c>
-      <c r="D65" s="247"/>
-      <c r="E65" s="125"/>
-      <c r="F65" s="125"/>
-      <c r="G65" s="89"/>
-      <c r="H65" s="125"/>
-      <c r="I65" s="91"/>
-      <c r="J65" s="67"/>
-      <c r="K65" s="67"/>
-      <c r="L65" s="67"/>
-      <c r="M65" s="67"/>
-      <c r="N65" s="67"/>
-      <c r="O65" s="67"/>
-      <c r="P65" s="67"/>
-      <c r="Q65" s="67"/>
-      <c r="R65" s="67"/>
-      <c r="S65" s="67"/>
-      <c r="T65" s="67"/>
-      <c r="U65" s="67"/>
-      <c r="V65" s="67"/>
-      <c r="W65" s="67"/>
-      <c r="X65" s="67"/>
-      <c r="Y65" s="67"/>
-      <c r="Z65" s="67"/>
-      <c r="AA65" s="67"/>
-      <c r="AB65" s="67"/>
-    </row>
-    <row r="66" spans="2:28" ht="9.75" customHeight="1">
+      <c r="D65" s="109"/>
+      <c r="E65" s="103"/>
+      <c r="F65" s="103"/>
+      <c r="G65" s="281"/>
+      <c r="H65" s="103"/>
+      <c r="I65" s="283"/>
+      <c r="J65" s="66"/>
+      <c r="K65" s="66"/>
+      <c r="L65" s="66"/>
+      <c r="M65" s="66"/>
+      <c r="N65" s="66"/>
+      <c r="O65" s="66"/>
+      <c r="P65" s="66"/>
+      <c r="Q65" s="66"/>
+      <c r="R65" s="66"/>
+      <c r="S65" s="66"/>
+      <c r="T65" s="66"/>
+      <c r="U65" s="66"/>
+      <c r="V65" s="66"/>
+      <c r="W65" s="66"/>
+      <c r="X65" s="66"/>
+      <c r="Y65" s="66"/>
+      <c r="Z65" s="66"/>
+      <c r="AA65" s="66"/>
+      <c r="AB65" s="66"/>
+    </row>
+    <row r="66" spans="2:28" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="59"/>
       <c r="C66" s="59"/>
       <c r="D66" s="59"/>
       <c r="E66" s="28"/>
       <c r="F66" s="28"/>
-      <c r="G66" s="246"/>
-      <c r="H66" s="246"/>
+      <c r="G66" s="107"/>
+      <c r="H66" s="107"/>
       <c r="I66" s="59"/>
-      <c r="J66" s="67"/>
-      <c r="K66" s="67"/>
-      <c r="L66" s="67"/>
-      <c r="M66" s="67"/>
-      <c r="N66" s="67"/>
-      <c r="O66" s="67"/>
-      <c r="P66" s="67"/>
-      <c r="Q66" s="67"/>
-      <c r="R66" s="67"/>
-      <c r="S66" s="67"/>
-      <c r="T66" s="67"/>
-      <c r="U66" s="67"/>
-      <c r="V66" s="67"/>
-      <c r="W66" s="67"/>
-      <c r="X66" s="67"/>
-      <c r="Y66" s="67"/>
-      <c r="Z66" s="67"/>
-      <c r="AA66" s="67"/>
-      <c r="AB66" s="67"/>
-    </row>
-    <row r="67" spans="2:28" ht="15" customHeight="1">
-      <c r="B67" s="236" t="s">
+      <c r="J66" s="66"/>
+      <c r="K66" s="66"/>
+      <c r="L66" s="66"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="66"/>
+      <c r="O66" s="66"/>
+      <c r="P66" s="66"/>
+      <c r="Q66" s="66"/>
+      <c r="R66" s="66"/>
+      <c r="S66" s="66"/>
+      <c r="T66" s="66"/>
+      <c r="U66" s="66"/>
+      <c r="V66" s="66"/>
+      <c r="W66" s="66"/>
+      <c r="X66" s="66"/>
+      <c r="Y66" s="66"/>
+      <c r="Z66" s="66"/>
+      <c r="AA66" s="66"/>
+      <c r="AB66" s="66"/>
+    </row>
+    <row r="67" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="236"/>
-      <c r="D67" s="236"/>
-      <c r="E67" s="236"/>
-      <c r="F67" s="236"/>
-      <c r="G67" s="236"/>
-      <c r="H67" s="236"/>
-      <c r="I67" s="236"/>
-      <c r="J67" s="67"/>
-      <c r="K67" s="67"/>
-      <c r="L67" s="67"/>
-      <c r="M67" s="67"/>
-      <c r="N67" s="67"/>
-      <c r="O67" s="67"/>
-      <c r="P67" s="67"/>
-      <c r="Q67" s="67"/>
-      <c r="R67" s="67"/>
-      <c r="S67" s="67"/>
-      <c r="T67" s="67"/>
-      <c r="U67" s="67"/>
-      <c r="V67" s="67"/>
-      <c r="W67" s="67"/>
-      <c r="X67" s="67"/>
-      <c r="Y67" s="67"/>
-      <c r="Z67" s="67"/>
-      <c r="AA67" s="67"/>
-      <c r="AB67" s="67"/>
-    </row>
-    <row r="68" spans="2:28" ht="15" customHeight="1">
+      <c r="C67" s="95"/>
+      <c r="D67" s="95"/>
+      <c r="E67" s="95"/>
+      <c r="F67" s="95"/>
+      <c r="G67" s="95"/>
+      <c r="H67" s="95"/>
+      <c r="I67" s="95"/>
+      <c r="J67" s="66"/>
+      <c r="K67" s="66"/>
+      <c r="L67" s="66"/>
+      <c r="M67" s="66"/>
+      <c r="N67" s="66"/>
+      <c r="O67" s="66"/>
+      <c r="P67" s="66"/>
+      <c r="Q67" s="66"/>
+      <c r="R67" s="66"/>
+      <c r="S67" s="66"/>
+      <c r="T67" s="66"/>
+      <c r="U67" s="66"/>
+      <c r="V67" s="66"/>
+      <c r="W67" s="66"/>
+      <c r="X67" s="66"/>
+      <c r="Y67" s="66"/>
+      <c r="Z67" s="66"/>
+      <c r="AA67" s="66"/>
+      <c r="AB67" s="66"/>
+    </row>
+    <row r="68" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="60"/>
       <c r="C68" s="60"/>
       <c r="D68" s="60"/>
       <c r="E68" s="29"/>
       <c r="F68" s="29"/>
-      <c r="G68" s="82"/>
-      <c r="H68" s="82"/>
+      <c r="G68" s="108"/>
+      <c r="H68" s="108"/>
       <c r="I68" s="60"/>
-      <c r="J68" s="67"/>
-      <c r="K68" s="67"/>
-      <c r="L68" s="67"/>
-      <c r="M68" s="67"/>
-      <c r="N68" s="67"/>
-      <c r="O68" s="67"/>
-      <c r="P68" s="67"/>
-      <c r="Q68" s="67"/>
-      <c r="R68" s="67"/>
-      <c r="S68" s="67"/>
-      <c r="T68" s="67"/>
-      <c r="U68" s="67"/>
-      <c r="V68" s="67"/>
-      <c r="W68" s="67"/>
-      <c r="X68" s="67"/>
-      <c r="Y68" s="67"/>
-      <c r="Z68" s="67"/>
-      <c r="AA68" s="67"/>
-      <c r="AB68" s="67"/>
-    </row>
-    <row r="69" spans="2:28" ht="36" customHeight="1">
-      <c r="B69" s="82" t="e" vm="1">
+      <c r="J68" s="66"/>
+      <c r="K68" s="66"/>
+      <c r="L68" s="66"/>
+      <c r="M68" s="66"/>
+      <c r="N68" s="66"/>
+      <c r="O68" s="66"/>
+      <c r="P68" s="66"/>
+      <c r="Q68" s="66"/>
+      <c r="R68" s="66"/>
+      <c r="S68" s="66"/>
+      <c r="T68" s="66"/>
+      <c r="U68" s="66"/>
+      <c r="V68" s="66"/>
+      <c r="W68" s="66"/>
+      <c r="X68" s="66"/>
+      <c r="Y68" s="66"/>
+      <c r="Z68" s="66"/>
+      <c r="AA68" s="66"/>
+      <c r="AB68" s="66"/>
+    </row>
+    <row r="69" spans="2:28" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="108" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C69" s="82"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
+      <c r="C69" s="108"/>
+      <c r="D69" s="108"/>
+      <c r="E69" s="108"/>
       <c r="F69" s="29"/>
-      <c r="G69" s="82"/>
-      <c r="H69" s="82"/>
+      <c r="G69" s="108"/>
+      <c r="H69" s="108"/>
       <c r="I69" s="60"/>
-      <c r="J69" s="67"/>
-      <c r="K69" s="67"/>
-      <c r="L69" s="67"/>
-      <c r="M69" s="67"/>
-      <c r="N69" s="67"/>
-      <c r="O69" s="67"/>
-      <c r="P69" s="67"/>
-      <c r="Q69" s="67"/>
-      <c r="R69" s="67"/>
-      <c r="S69" s="67"/>
-      <c r="T69" s="67"/>
-      <c r="U69" s="67"/>
-      <c r="V69" s="67"/>
-      <c r="W69" s="67"/>
-      <c r="X69" s="67"/>
-      <c r="Y69" s="67"/>
-      <c r="Z69" s="67"/>
-      <c r="AA69" s="67"/>
-      <c r="AB69" s="67"/>
-    </row>
-    <row r="70" spans="2:28" ht="36" customHeight="1">
-      <c r="B70" s="83"/>
-      <c r="C70" s="83"/>
-      <c r="D70" s="83"/>
-      <c r="E70" s="83"/>
+      <c r="J69" s="66"/>
+      <c r="K69" s="66"/>
+      <c r="L69" s="66"/>
+      <c r="M69" s="66"/>
+      <c r="N69" s="66"/>
+      <c r="O69" s="66"/>
+      <c r="P69" s="66"/>
+      <c r="Q69" s="66"/>
+      <c r="R69" s="66"/>
+      <c r="S69" s="66"/>
+      <c r="T69" s="66"/>
+      <c r="U69" s="66"/>
+      <c r="V69" s="66"/>
+      <c r="W69" s="66"/>
+      <c r="X69" s="66"/>
+      <c r="Y69" s="66"/>
+      <c r="Z69" s="66"/>
+      <c r="AA69" s="66"/>
+      <c r="AB69" s="66"/>
+    </row>
+    <row r="70" spans="2:28" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="276"/>
+      <c r="C70" s="276"/>
+      <c r="D70" s="276"/>
+      <c r="E70" s="276"/>
       <c r="F70" s="20"/>
-      <c r="G70" s="61"/>
       <c r="H70" s="47">
         <v>46215</v>
       </c>
-      <c r="I70" s="67"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="67"/>
-      <c r="L70" s="67"/>
-      <c r="M70" s="67"/>
-      <c r="N70" s="67"/>
-      <c r="O70" s="67"/>
-      <c r="P70" s="67"/>
-      <c r="Q70" s="67"/>
-      <c r="R70" s="67"/>
-      <c r="S70" s="67"/>
-      <c r="T70" s="67"/>
-      <c r="U70" s="67"/>
-      <c r="V70" s="67"/>
-      <c r="W70" s="67"/>
-      <c r="X70" s="67"/>
-      <c r="Y70" s="67"/>
-      <c r="Z70" s="67"/>
-      <c r="AA70" s="67"/>
-      <c r="AB70" s="67"/>
-    </row>
-    <row r="71" spans="2:28" ht="15" customHeight="1">
-      <c r="B71" s="235" t="s">
+      <c r="I70" s="66"/>
+      <c r="J70" s="66"/>
+      <c r="K70" s="66"/>
+      <c r="L70" s="66"/>
+      <c r="M70" s="66"/>
+      <c r="N70" s="66"/>
+      <c r="O70" s="66"/>
+      <c r="P70" s="66"/>
+      <c r="Q70" s="66"/>
+      <c r="R70" s="66"/>
+      <c r="S70" s="66"/>
+      <c r="T70" s="66"/>
+      <c r="U70" s="66"/>
+      <c r="V70" s="66"/>
+      <c r="W70" s="66"/>
+      <c r="X70" s="66"/>
+      <c r="Y70" s="66"/>
+      <c r="Z70" s="66"/>
+      <c r="AA70" s="66"/>
+      <c r="AB70" s="66"/>
+    </row>
+    <row r="71" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="C71" s="235"/>
-      <c r="D71" s="235"/>
-      <c r="E71" s="235"/>
+      <c r="C71" s="91"/>
+      <c r="D71" s="91"/>
+      <c r="E71" s="91"/>
       <c r="F71" s="59"/>
-      <c r="G71" s="61"/>
       <c r="H71" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="I71" s="67"/>
-      <c r="J71" s="67"/>
-      <c r="K71" s="67"/>
-      <c r="L71" s="67"/>
-      <c r="M71" s="67"/>
-      <c r="N71" s="67"/>
-      <c r="O71" s="67"/>
-      <c r="P71" s="67"/>
-      <c r="Q71" s="67"/>
-      <c r="R71" s="67"/>
-      <c r="S71" s="67"/>
-      <c r="T71" s="67"/>
-      <c r="U71" s="67"/>
-      <c r="V71" s="67"/>
-      <c r="W71" s="67"/>
-      <c r="X71" s="67"/>
-      <c r="Y71" s="67"/>
-      <c r="Z71" s="67"/>
-      <c r="AA71" s="67"/>
-      <c r="AB71" s="67"/>
-    </row>
-    <row r="72" spans="2:28" ht="14.45">
+      <c r="I71" s="66"/>
+      <c r="J71" s="66"/>
+      <c r="K71" s="66"/>
+      <c r="L71" s="66"/>
+      <c r="M71" s="66"/>
+      <c r="N71" s="66"/>
+      <c r="O71" s="66"/>
+      <c r="P71" s="66"/>
+      <c r="Q71" s="66"/>
+      <c r="R71" s="66"/>
+      <c r="S71" s="66"/>
+      <c r="T71" s="66"/>
+      <c r="U71" s="66"/>
+      <c r="V71" s="66"/>
+      <c r="W71" s="66"/>
+      <c r="X71" s="66"/>
+      <c r="Y71" s="66"/>
+      <c r="Z71" s="66"/>
+      <c r="AA71" s="66"/>
+      <c r="AB71" s="66"/>
+    </row>
+    <row r="72" spans="2:28" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B72" s="7"/>
-      <c r="C72" s="67"/>
-      <c r="D72" s="67"/>
+      <c r="C72" s="66"/>
+      <c r="D72" s="66"/>
       <c r="E72" s="20"/>
       <c r="F72" s="20"/>
-      <c r="G72" s="77"/>
-      <c r="H72" s="93"/>
-      <c r="I72" s="67"/>
-      <c r="J72" s="67"/>
-      <c r="K72" s="67"/>
-      <c r="L72" s="67"/>
-      <c r="M72" s="67"/>
-      <c r="N72" s="67"/>
-      <c r="O72" s="67"/>
-      <c r="P72" s="67"/>
-      <c r="Q72" s="67"/>
-      <c r="R72" s="67"/>
-      <c r="S72" s="67"/>
-      <c r="T72" s="67"/>
-      <c r="U72" s="67"/>
-      <c r="V72" s="67"/>
-      <c r="W72" s="67"/>
-      <c r="X72" s="67"/>
-      <c r="Y72" s="67"/>
-      <c r="Z72" s="67"/>
-      <c r="AA72" s="67"/>
-      <c r="AB72" s="67"/>
-    </row>
-    <row r="73" spans="2:28" ht="30" customHeight="1">
-      <c r="B73" s="86"/>
-      <c r="C73" s="86"/>
-      <c r="D73" s="86"/>
-      <c r="E73" s="86"/>
+      <c r="G72" s="111"/>
+      <c r="H72" s="233"/>
+      <c r="I72" s="66"/>
+      <c r="J72" s="66"/>
+      <c r="K72" s="66"/>
+      <c r="L72" s="66"/>
+      <c r="M72" s="66"/>
+      <c r="N72" s="66"/>
+      <c r="O72" s="66"/>
+      <c r="P72" s="66"/>
+      <c r="Q72" s="66"/>
+      <c r="R72" s="66"/>
+      <c r="S72" s="66"/>
+      <c r="T72" s="66"/>
+      <c r="U72" s="66"/>
+      <c r="V72" s="66"/>
+      <c r="W72" s="66"/>
+      <c r="X72" s="66"/>
+      <c r="Y72" s="66"/>
+      <c r="Z72" s="66"/>
+      <c r="AA72" s="66"/>
+      <c r="AB72" s="66"/>
+    </row>
+    <row r="73" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="278"/>
+      <c r="C73" s="278"/>
+      <c r="D73" s="278"/>
+      <c r="E73" s="278"/>
       <c r="F73" s="20"/>
-      <c r="G73" s="61"/>
-      <c r="H73" s="84"/>
-      <c r="I73" s="84"/>
-      <c r="J73" s="67"/>
-      <c r="K73" s="67"/>
-      <c r="L73" s="67"/>
-      <c r="M73" s="67"/>
-      <c r="N73" s="67"/>
-      <c r="O73" s="67"/>
-      <c r="P73" s="67"/>
-      <c r="Q73" s="67"/>
-      <c r="R73" s="67"/>
-      <c r="S73" s="67"/>
-      <c r="T73" s="67"/>
-      <c r="U73" s="67"/>
-      <c r="V73" s="67"/>
-      <c r="W73" s="67"/>
-      <c r="X73" s="67"/>
-      <c r="Y73" s="67"/>
-      <c r="Z73" s="67"/>
-      <c r="AA73" s="67"/>
-      <c r="AB73" s="67"/>
-    </row>
-    <row r="74" spans="2:28" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B74" s="87"/>
-      <c r="C74" s="87"/>
-      <c r="D74" s="87"/>
-      <c r="E74" s="87"/>
+      <c r="H73" s="238"/>
+      <c r="I73" s="238"/>
+      <c r="J73" s="66"/>
+      <c r="K73" s="66"/>
+      <c r="L73" s="66"/>
+      <c r="M73" s="66"/>
+      <c r="N73" s="66"/>
+      <c r="O73" s="66"/>
+      <c r="P73" s="66"/>
+      <c r="Q73" s="66"/>
+      <c r="R73" s="66"/>
+      <c r="S73" s="66"/>
+      <c r="T73" s="66"/>
+      <c r="U73" s="66"/>
+      <c r="V73" s="66"/>
+      <c r="W73" s="66"/>
+      <c r="X73" s="66"/>
+      <c r="Y73" s="66"/>
+      <c r="Z73" s="66"/>
+      <c r="AA73" s="66"/>
+      <c r="AB73" s="66"/>
+    </row>
+    <row r="74" spans="2:28" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="279"/>
+      <c r="C74" s="279"/>
+      <c r="D74" s="279"/>
+      <c r="E74" s="279"/>
       <c r="F74" s="20"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="85"/>
-      <c r="I74" s="85"/>
-      <c r="J74" s="67"/>
-      <c r="K74" s="67"/>
-      <c r="L74" s="67"/>
-      <c r="M74" s="67"/>
-      <c r="N74" s="67"/>
-      <c r="O74" s="67"/>
-      <c r="P74" s="67"/>
-      <c r="Q74" s="67"/>
-      <c r="R74" s="67"/>
-      <c r="S74" s="67"/>
-      <c r="T74" s="67"/>
-      <c r="U74" s="67"/>
-      <c r="V74" s="67"/>
-      <c r="W74" s="67"/>
-      <c r="X74" s="67"/>
-      <c r="Y74" s="67"/>
-      <c r="Z74" s="67"/>
-      <c r="AA74" s="67"/>
-      <c r="AB74" s="67"/>
-    </row>
-    <row r="75" spans="2:28" ht="15.75" customHeight="1">
+      <c r="H74" s="277"/>
+      <c r="I74" s="277"/>
+      <c r="J74" s="66"/>
+      <c r="K74" s="66"/>
+      <c r="L74" s="66"/>
+      <c r="M74" s="66"/>
+      <c r="N74" s="66"/>
+      <c r="O74" s="66"/>
+      <c r="P74" s="66"/>
+      <c r="Q74" s="66"/>
+      <c r="R74" s="66"/>
+      <c r="S74" s="66"/>
+      <c r="T74" s="66"/>
+      <c r="U74" s="66"/>
+      <c r="V74" s="66"/>
+      <c r="W74" s="66"/>
+      <c r="X74" s="66"/>
+      <c r="Y74" s="66"/>
+      <c r="Z74" s="66"/>
+      <c r="AA74" s="66"/>
+      <c r="AB74" s="66"/>
+    </row>
+    <row r="75" spans="2:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="7"/>
       <c r="C75" s="18" t="s">
         <v>106</v>
@@ -6924,160 +6868,159 @@
       <c r="D75" s="18"/>
       <c r="E75" s="20"/>
       <c r="F75" s="20"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="235" t="s">
+      <c r="H75" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="I75" s="235"/>
-      <c r="J75" s="67"/>
-      <c r="K75" s="67"/>
-      <c r="L75" s="67"/>
-      <c r="M75" s="67"/>
-      <c r="N75" s="67"/>
-      <c r="O75" s="67"/>
-      <c r="P75" s="67"/>
-      <c r="Q75" s="67"/>
-      <c r="R75" s="67"/>
-      <c r="S75" s="67"/>
-      <c r="T75" s="67"/>
-      <c r="U75" s="67"/>
-      <c r="V75" s="67"/>
-      <c r="W75" s="67"/>
-      <c r="X75" s="67"/>
-      <c r="Y75" s="67"/>
-      <c r="Z75" s="67"/>
-      <c r="AA75" s="67"/>
-      <c r="AB75" s="67"/>
-    </row>
-    <row r="76" spans="2:28" ht="7.15" customHeight="1">
+      <c r="I75" s="91"/>
+      <c r="J75" s="66"/>
+      <c r="K75" s="66"/>
+      <c r="L75" s="66"/>
+      <c r="M75" s="66"/>
+      <c r="N75" s="66"/>
+      <c r="O75" s="66"/>
+      <c r="P75" s="66"/>
+      <c r="Q75" s="66"/>
+      <c r="R75" s="66"/>
+      <c r="S75" s="66"/>
+      <c r="T75" s="66"/>
+      <c r="U75" s="66"/>
+      <c r="V75" s="66"/>
+      <c r="W75" s="66"/>
+      <c r="X75" s="66"/>
+      <c r="Y75" s="66"/>
+      <c r="Z75" s="66"/>
+      <c r="AA75" s="66"/>
+      <c r="AB75" s="66"/>
+    </row>
+    <row r="76" spans="2:28" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="7"/>
       <c r="C76" s="18"/>
       <c r="D76" s="18"/>
       <c r="E76" s="20"/>
       <c r="F76" s="20"/>
-      <c r="G76" s="77"/>
-      <c r="H76" s="246"/>
+      <c r="G76" s="111"/>
+      <c r="H76" s="107"/>
       <c r="I76" s="59"/>
-      <c r="J76" s="67"/>
-      <c r="K76" s="67"/>
-      <c r="L76" s="67"/>
-      <c r="M76" s="67"/>
-      <c r="N76" s="67"/>
-      <c r="O76" s="67"/>
-      <c r="P76" s="67"/>
-      <c r="Q76" s="67"/>
-      <c r="R76" s="67"/>
-      <c r="S76" s="67"/>
-      <c r="T76" s="67"/>
-      <c r="U76" s="67"/>
-      <c r="V76" s="67"/>
-      <c r="W76" s="67"/>
-      <c r="X76" s="67"/>
-      <c r="Y76" s="67"/>
-      <c r="Z76" s="67"/>
-      <c r="AA76" s="67"/>
-      <c r="AB76" s="67"/>
-    </row>
-    <row r="77" spans="2:28" ht="18" customHeight="1">
-      <c r="B77" s="248" t="s">
+      <c r="J76" s="66"/>
+      <c r="K76" s="66"/>
+      <c r="L76" s="66"/>
+      <c r="M76" s="66"/>
+      <c r="N76" s="66"/>
+      <c r="O76" s="66"/>
+      <c r="P76" s="66"/>
+      <c r="Q76" s="66"/>
+      <c r="R76" s="66"/>
+      <c r="S76" s="66"/>
+      <c r="T76" s="66"/>
+      <c r="U76" s="66"/>
+      <c r="V76" s="66"/>
+      <c r="W76" s="66"/>
+      <c r="X76" s="66"/>
+      <c r="Y76" s="66"/>
+      <c r="Z76" s="66"/>
+      <c r="AA76" s="66"/>
+      <c r="AB76" s="66"/>
+    </row>
+    <row r="77" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="110" t="s">
         <v>108</v>
       </c>
-      <c r="C77" s="248"/>
-      <c r="D77" s="248"/>
-      <c r="E77" s="248"/>
-      <c r="F77" s="248"/>
-      <c r="G77" s="248"/>
-      <c r="H77" s="248"/>
-      <c r="I77" s="248"/>
-      <c r="J77" s="67"/>
-      <c r="K77" s="67"/>
-      <c r="L77" s="67"/>
-      <c r="M77" s="67"/>
-      <c r="N77" s="67"/>
-      <c r="O77" s="67"/>
-      <c r="P77" s="67"/>
-      <c r="Q77" s="67"/>
-      <c r="R77" s="67"/>
-      <c r="S77" s="67"/>
-      <c r="T77" s="67"/>
-      <c r="U77" s="67"/>
-      <c r="V77" s="67"/>
-      <c r="W77" s="67"/>
-      <c r="X77" s="67"/>
-      <c r="Y77" s="67"/>
-      <c r="Z77" s="67"/>
-      <c r="AA77" s="67"/>
-      <c r="AB77" s="67"/>
-    </row>
-    <row r="78" spans="2:28" ht="14.45">
-      <c r="B78" s="248"/>
-      <c r="C78" s="248"/>
-      <c r="D78" s="248"/>
-      <c r="E78" s="248"/>
-      <c r="F78" s="248"/>
-      <c r="G78" s="248"/>
-      <c r="H78" s="248"/>
-      <c r="I78" s="248"/>
-      <c r="J78" s="67"/>
-      <c r="K78" s="67"/>
-      <c r="L78" s="67"/>
-      <c r="M78" s="67"/>
-      <c r="N78" s="67"/>
-      <c r="O78" s="67"/>
-      <c r="P78" s="67"/>
-      <c r="Q78" s="67"/>
-      <c r="R78" s="67"/>
-      <c r="S78" s="67"/>
-      <c r="T78" s="67"/>
-      <c r="U78" s="67"/>
-      <c r="V78" s="67"/>
-      <c r="W78" s="67"/>
-      <c r="X78" s="67"/>
-      <c r="Y78" s="67"/>
-      <c r="Z78" s="67"/>
-      <c r="AA78" s="67"/>
-      <c r="AB78" s="67"/>
-    </row>
-    <row r="79" spans="2:28" ht="8.4499999999999993" customHeight="1">
-      <c r="B79" s="62"/>
-      <c r="C79" s="62"/>
-      <c r="D79" s="62"/>
-      <c r="E79" s="62"/>
-      <c r="F79" s="62"/>
-      <c r="G79" s="249"/>
-      <c r="H79" s="249"/>
-      <c r="I79" s="62"/>
-      <c r="J79" s="67"/>
-      <c r="K79" s="67"/>
-      <c r="L79" s="67"/>
-      <c r="M79" s="67"/>
-      <c r="N79" s="67"/>
-      <c r="O79" s="67"/>
-      <c r="P79" s="67"/>
-      <c r="Q79" s="67"/>
-      <c r="R79" s="67"/>
-      <c r="S79" s="67"/>
-      <c r="T79" s="67"/>
-      <c r="U79" s="67"/>
-      <c r="V79" s="67"/>
-      <c r="W79" s="67"/>
-      <c r="X79" s="67"/>
-      <c r="Y79" s="67"/>
-      <c r="Z79" s="67"/>
-      <c r="AA79" s="67"/>
-      <c r="AB79" s="67"/>
-    </row>
-    <row r="80" spans="2:28" ht="24" customHeight="1">
-      <c r="B80" s="229" t="s">
+      <c r="C77" s="110"/>
+      <c r="D77" s="110"/>
+      <c r="E77" s="110"/>
+      <c r="F77" s="110"/>
+      <c r="G77" s="110"/>
+      <c r="H77" s="110"/>
+      <c r="I77" s="110"/>
+      <c r="J77" s="66"/>
+      <c r="K77" s="66"/>
+      <c r="L77" s="66"/>
+      <c r="M77" s="66"/>
+      <c r="N77" s="66"/>
+      <c r="O77" s="66"/>
+      <c r="P77" s="66"/>
+      <c r="Q77" s="66"/>
+      <c r="R77" s="66"/>
+      <c r="S77" s="66"/>
+      <c r="T77" s="66"/>
+      <c r="U77" s="66"/>
+      <c r="V77" s="66"/>
+      <c r="W77" s="66"/>
+      <c r="X77" s="66"/>
+      <c r="Y77" s="66"/>
+      <c r="Z77" s="66"/>
+      <c r="AA77" s="66"/>
+      <c r="AB77" s="66"/>
+    </row>
+    <row r="78" spans="2:28" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B78" s="110"/>
+      <c r="C78" s="110"/>
+      <c r="D78" s="110"/>
+      <c r="E78" s="110"/>
+      <c r="F78" s="110"/>
+      <c r="G78" s="110"/>
+      <c r="H78" s="110"/>
+      <c r="I78" s="110"/>
+      <c r="J78" s="66"/>
+      <c r="K78" s="66"/>
+      <c r="L78" s="66"/>
+      <c r="M78" s="66"/>
+      <c r="N78" s="66"/>
+      <c r="O78" s="66"/>
+      <c r="P78" s="66"/>
+      <c r="Q78" s="66"/>
+      <c r="R78" s="66"/>
+      <c r="S78" s="66"/>
+      <c r="T78" s="66"/>
+      <c r="U78" s="66"/>
+      <c r="V78" s="66"/>
+      <c r="W78" s="66"/>
+      <c r="X78" s="66"/>
+      <c r="Y78" s="66"/>
+      <c r="Z78" s="66"/>
+      <c r="AA78" s="66"/>
+      <c r="AB78" s="66"/>
+    </row>
+    <row r="79" spans="2:28" ht="8.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="61"/>
+      <c r="C79" s="61"/>
+      <c r="D79" s="61"/>
+      <c r="E79" s="61"/>
+      <c r="F79" s="61"/>
+      <c r="G79" s="112"/>
+      <c r="H79" s="112"/>
+      <c r="I79" s="61"/>
+      <c r="J79" s="66"/>
+      <c r="K79" s="66"/>
+      <c r="L79" s="66"/>
+      <c r="M79" s="66"/>
+      <c r="N79" s="66"/>
+      <c r="O79" s="66"/>
+      <c r="P79" s="66"/>
+      <c r="Q79" s="66"/>
+      <c r="R79" s="66"/>
+      <c r="S79" s="66"/>
+      <c r="T79" s="66"/>
+      <c r="U79" s="66"/>
+      <c r="V79" s="66"/>
+      <c r="W79" s="66"/>
+      <c r="X79" s="66"/>
+      <c r="Y79" s="66"/>
+      <c r="Z79" s="66"/>
+      <c r="AA79" s="66"/>
+      <c r="AB79" s="66"/>
+    </row>
+    <row r="80" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="C80" s="230"/>
-      <c r="D80" s="230"/>
-      <c r="E80" s="230"/>
-      <c r="F80" s="230"/>
-      <c r="G80" s="230"/>
-      <c r="H80" s="230"/>
-      <c r="I80" s="231"/>
+      <c r="C80" s="86"/>
+      <c r="D80" s="86"/>
+      <c r="E80" s="86"/>
+      <c r="F80" s="86"/>
+      <c r="G80" s="86"/>
+      <c r="H80" s="86"/>
+      <c r="I80" s="87"/>
       <c r="J80" s="8"/>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -7098,17 +7041,17 @@
       <c r="AA80" s="7"/>
       <c r="AB80" s="7"/>
     </row>
-    <row r="81" spans="2:28" ht="13.5" customHeight="1">
-      <c r="B81" s="232" t="s">
+    <row r="81" spans="2:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="C81" s="233"/>
-      <c r="D81" s="233"/>
-      <c r="E81" s="233"/>
-      <c r="F81" s="233"/>
-      <c r="G81" s="233"/>
-      <c r="H81" s="233"/>
-      <c r="I81" s="234"/>
+      <c r="C81" s="89"/>
+      <c r="D81" s="89"/>
+      <c r="E81" s="89"/>
+      <c r="F81" s="89"/>
+      <c r="G81" s="89"/>
+      <c r="H81" s="89"/>
+      <c r="I81" s="90"/>
       <c r="J81" s="8"/>
       <c r="K81" s="19"/>
       <c r="L81" s="7"/>
@@ -7129,23 +7072,19 @@
       <c r="AA81" s="7"/>
       <c r="AB81" s="7"/>
     </row>
-    <row r="82" spans="2:28" s="8" customFormat="1" ht="241.5" customHeight="1" thickBot="1">
-      <c r="B82" s="79"/>
-      <c r="C82" s="80"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="80"/>
-      <c r="F82" s="80"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="80"/>
-      <c r="I82" s="81"/>
-    </row>
-    <row r="83" spans="2:28" ht="14.45" hidden="1">
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
-      <c r="D83" s="61"/>
-      <c r="G83" s="77"/>
-      <c r="H83" s="77"/>
-      <c r="I83" s="61"/>
+    <row r="82" spans="2:28" s="8" customFormat="1" ht="241.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="273"/>
+      <c r="C82" s="274"/>
+      <c r="D82" s="274"/>
+      <c r="E82" s="274"/>
+      <c r="F82" s="274"/>
+      <c r="G82" s="274"/>
+      <c r="H82" s="274"/>
+      <c r="I82" s="275"/>
+    </row>
+    <row r="83" spans="2:28" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G83" s="111"/>
+      <c r="H83" s="111"/>
       <c r="J83" s="8"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -7166,935 +7105,146 @@
       <c r="AA83" s="7"/>
       <c r="AB83" s="7"/>
     </row>
-    <row r="84" spans="2:28" ht="14.45" hidden="1">
-      <c r="B84" s="61"/>
-      <c r="C84" s="61"/>
-      <c r="D84" s="61"/>
-      <c r="G84" s="77"/>
-      <c r="H84" s="77"/>
-      <c r="I84" s="61"/>
-      <c r="J84" s="61"/>
-      <c r="K84" s="61"/>
-      <c r="L84" s="61"/>
-      <c r="M84" s="61"/>
-      <c r="N84" s="61"/>
-      <c r="O84" s="61"/>
-      <c r="P84" s="61"/>
-      <c r="Q84" s="61"/>
-      <c r="R84" s="61"/>
-      <c r="S84" s="61"/>
-      <c r="T84" s="61"/>
-      <c r="U84" s="61"/>
-      <c r="V84" s="61"/>
-      <c r="W84" s="61"/>
-      <c r="X84" s="61"/>
-      <c r="Y84" s="61"/>
-      <c r="Z84" s="61"/>
-      <c r="AA84" s="61"/>
-    </row>
-    <row r="85" spans="2:28" ht="14.45" hidden="1">
-      <c r="B85" s="61"/>
-      <c r="C85" s="61"/>
-      <c r="D85" s="61"/>
-      <c r="G85" s="77"/>
-      <c r="H85" s="77"/>
-      <c r="I85" s="61"/>
-      <c r="J85" s="61"/>
-      <c r="K85" s="61"/>
-      <c r="L85" s="61"/>
-      <c r="M85" s="61"/>
-      <c r="N85" s="61"/>
-      <c r="O85" s="61"/>
-      <c r="P85" s="61"/>
-      <c r="Q85" s="61"/>
-      <c r="R85" s="61"/>
-      <c r="S85" s="61"/>
-      <c r="T85" s="61"/>
-      <c r="U85" s="61"/>
-      <c r="V85" s="61"/>
-      <c r="W85" s="61"/>
-      <c r="X85" s="61"/>
-      <c r="Y85" s="61"/>
-      <c r="Z85" s="61"/>
-      <c r="AA85" s="61"/>
-    </row>
-    <row r="86" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B86" s="61"/>
-      <c r="C86" s="61"/>
-      <c r="D86" s="61"/>
-      <c r="G86" s="77"/>
-      <c r="H86" s="77"/>
-      <c r="I86" s="61"/>
-      <c r="J86" s="61"/>
-      <c r="K86" s="61"/>
-      <c r="L86" s="61"/>
-      <c r="M86" s="61"/>
-      <c r="N86" s="61"/>
-      <c r="O86" s="61"/>
-      <c r="P86" s="61"/>
-      <c r="Q86" s="61"/>
-      <c r="R86" s="61"/>
-      <c r="S86" s="61"/>
-      <c r="T86" s="61"/>
-      <c r="U86" s="61"/>
-      <c r="V86" s="61"/>
-      <c r="W86" s="61"/>
-      <c r="X86" s="61"/>
-      <c r="Y86" s="61"/>
-      <c r="Z86" s="61"/>
-      <c r="AA86" s="61"/>
-    </row>
-    <row r="87" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B87" s="61"/>
-      <c r="C87" s="61"/>
-      <c r="D87" s="61"/>
-      <c r="G87" s="77"/>
-      <c r="H87" s="77"/>
-      <c r="I87" s="61"/>
-      <c r="J87" s="61"/>
-      <c r="K87" s="61"/>
-      <c r="L87" s="61"/>
-      <c r="M87" s="61"/>
-      <c r="N87" s="61"/>
-      <c r="O87" s="61"/>
-      <c r="P87" s="61"/>
-      <c r="Q87" s="61"/>
-      <c r="R87" s="61"/>
-      <c r="S87" s="61"/>
-      <c r="T87" s="61"/>
-      <c r="U87" s="61"/>
-      <c r="V87" s="61"/>
-      <c r="W87" s="61"/>
-      <c r="X87" s="61"/>
-      <c r="Y87" s="61"/>
-      <c r="Z87" s="61"/>
-      <c r="AA87" s="61"/>
-    </row>
-    <row r="88" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B88" s="61"/>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="G88" s="77"/>
-      <c r="H88" s="77"/>
-      <c r="I88" s="61"/>
-      <c r="J88" s="61"/>
-      <c r="K88" s="61"/>
-      <c r="L88" s="61"/>
-      <c r="M88" s="61"/>
-      <c r="N88" s="61"/>
-      <c r="O88" s="61"/>
-      <c r="P88" s="61"/>
-      <c r="Q88" s="61"/>
-      <c r="R88" s="61"/>
-      <c r="S88" s="61"/>
-      <c r="T88" s="61"/>
-      <c r="U88" s="61"/>
-      <c r="V88" s="61"/>
-      <c r="W88" s="61"/>
-      <c r="X88" s="61"/>
-      <c r="Y88" s="61"/>
-      <c r="Z88" s="61"/>
-      <c r="AA88" s="61"/>
-    </row>
-    <row r="89" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B89" s="61"/>
-      <c r="C89" s="61"/>
-      <c r="D89" s="61"/>
-      <c r="G89" s="77"/>
-      <c r="H89" s="77"/>
-      <c r="I89" s="61"/>
-      <c r="J89" s="61"/>
-      <c r="K89" s="61"/>
-      <c r="L89" s="61"/>
-      <c r="M89" s="61"/>
-      <c r="N89" s="61"/>
-      <c r="O89" s="61"/>
-      <c r="P89" s="61"/>
-      <c r="Q89" s="61"/>
-      <c r="R89" s="61"/>
-      <c r="S89" s="61"/>
-      <c r="T89" s="61"/>
-      <c r="U89" s="61"/>
-      <c r="V89" s="61"/>
-      <c r="W89" s="61"/>
-      <c r="X89" s="61"/>
-      <c r="Y89" s="61"/>
-      <c r="Z89" s="61"/>
-      <c r="AA89" s="61"/>
-    </row>
-    <row r="90" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B90" s="61"/>
-      <c r="C90" s="61"/>
-      <c r="D90" s="61"/>
-      <c r="G90" s="77"/>
-      <c r="H90" s="77"/>
-      <c r="I90" s="61"/>
-      <c r="J90" s="61"/>
-      <c r="K90" s="61"/>
-      <c r="L90" s="61"/>
-      <c r="M90" s="61"/>
-      <c r="N90" s="61"/>
-      <c r="O90" s="61"/>
-      <c r="P90" s="61"/>
-      <c r="Q90" s="61"/>
-      <c r="R90" s="61"/>
-      <c r="S90" s="61"/>
-      <c r="T90" s="61"/>
-      <c r="U90" s="61"/>
-      <c r="V90" s="61"/>
-      <c r="W90" s="61"/>
-      <c r="X90" s="61"/>
-      <c r="Y90" s="61"/>
-      <c r="Z90" s="61"/>
-      <c r="AA90" s="61"/>
-    </row>
-    <row r="91" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B91" s="61"/>
-      <c r="C91" s="61"/>
-      <c r="D91" s="61"/>
-      <c r="G91" s="77"/>
-      <c r="H91" s="77"/>
-      <c r="I91" s="61"/>
-      <c r="J91" s="61"/>
-      <c r="K91" s="61"/>
-      <c r="L91" s="61"/>
-      <c r="M91" s="61"/>
-      <c r="N91" s="61"/>
-      <c r="O91" s="61"/>
-      <c r="P91" s="61"/>
-      <c r="Q91" s="61"/>
-      <c r="R91" s="61"/>
-      <c r="S91" s="61"/>
-      <c r="T91" s="61"/>
-      <c r="U91" s="61"/>
-      <c r="V91" s="61"/>
-      <c r="W91" s="61"/>
-      <c r="X91" s="61"/>
-      <c r="Y91" s="61"/>
-      <c r="Z91" s="61"/>
-      <c r="AA91" s="61"/>
-    </row>
-    <row r="92" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B92" s="61"/>
-      <c r="C92" s="61"/>
-      <c r="D92" s="61"/>
-      <c r="G92" s="77"/>
-      <c r="H92" s="77"/>
-      <c r="I92" s="61"/>
-      <c r="J92" s="61"/>
-      <c r="K92" s="61"/>
-      <c r="L92" s="61"/>
-      <c r="M92" s="61"/>
-      <c r="N92" s="61"/>
-      <c r="O92" s="61"/>
-      <c r="P92" s="61"/>
-      <c r="Q92" s="61"/>
-      <c r="R92" s="61"/>
-      <c r="S92" s="61"/>
-      <c r="T92" s="61"/>
-      <c r="U92" s="61"/>
-      <c r="V92" s="61"/>
-      <c r="W92" s="61"/>
-      <c r="X92" s="61"/>
-      <c r="Y92" s="61"/>
-      <c r="Z92" s="61"/>
-      <c r="AA92" s="61"/>
-    </row>
-    <row r="93" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B93" s="61"/>
-      <c r="C93" s="61"/>
-      <c r="D93" s="61"/>
-      <c r="G93" s="77"/>
-      <c r="H93" s="77"/>
-      <c r="I93" s="61"/>
-      <c r="J93" s="61"/>
-      <c r="K93" s="61"/>
-      <c r="L93" s="61"/>
-      <c r="M93" s="61"/>
-      <c r="N93" s="61"/>
-      <c r="O93" s="61"/>
-      <c r="P93" s="61"/>
-      <c r="Q93" s="61"/>
-      <c r="R93" s="61"/>
-      <c r="S93" s="61"/>
-      <c r="T93" s="61"/>
-      <c r="U93" s="61"/>
-      <c r="V93" s="61"/>
-      <c r="W93" s="61"/>
-      <c r="X93" s="61"/>
-      <c r="Y93" s="61"/>
-      <c r="Z93" s="61"/>
-      <c r="AA93" s="61"/>
-    </row>
-    <row r="94" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
-      <c r="D94" s="61"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="77"/>
-      <c r="I94" s="61"/>
-      <c r="J94" s="61"/>
-      <c r="K94" s="61"/>
-      <c r="L94" s="61"/>
-      <c r="M94" s="61"/>
-      <c r="N94" s="61"/>
-      <c r="O94" s="61"/>
-      <c r="P94" s="61"/>
-      <c r="Q94" s="61"/>
-      <c r="R94" s="61"/>
-      <c r="S94" s="61"/>
-      <c r="T94" s="61"/>
-      <c r="U94" s="61"/>
-      <c r="V94" s="61"/>
-      <c r="W94" s="61"/>
-      <c r="X94" s="61"/>
-      <c r="Y94" s="61"/>
-      <c r="Z94" s="61"/>
-      <c r="AA94" s="61"/>
-    </row>
-    <row r="95" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B95" s="61"/>
-      <c r="C95" s="61"/>
-      <c r="D95" s="61"/>
-      <c r="G95" s="77"/>
-      <c r="H95" s="77"/>
-      <c r="I95" s="61"/>
-      <c r="J95" s="61"/>
-      <c r="K95" s="61"/>
-      <c r="L95" s="61"/>
-      <c r="M95" s="61"/>
-      <c r="N95" s="61"/>
-      <c r="O95" s="61"/>
-      <c r="P95" s="61"/>
-      <c r="Q95" s="61"/>
-      <c r="R95" s="61"/>
-      <c r="S95" s="61"/>
-      <c r="T95" s="61"/>
-      <c r="U95" s="61"/>
-      <c r="V95" s="61"/>
-      <c r="W95" s="61"/>
-      <c r="X95" s="61"/>
-      <c r="Y95" s="61"/>
-      <c r="Z95" s="61"/>
-      <c r="AA95" s="61"/>
-    </row>
-    <row r="96" spans="2:28" ht="15" hidden="1" customHeight="1">
-      <c r="B96" s="61"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
-      <c r="G96" s="77"/>
-      <c r="H96" s="77"/>
-      <c r="I96" s="61"/>
-      <c r="J96" s="61"/>
-      <c r="K96" s="61"/>
-      <c r="L96" s="61"/>
-      <c r="M96" s="61"/>
-      <c r="N96" s="61"/>
-      <c r="O96" s="61"/>
-      <c r="P96" s="61"/>
-      <c r="Q96" s="61"/>
-      <c r="R96" s="61"/>
-      <c r="S96" s="61"/>
-      <c r="T96" s="61"/>
-      <c r="U96" s="61"/>
-      <c r="V96" s="61"/>
-      <c r="W96" s="61"/>
-      <c r="X96" s="61"/>
-      <c r="Y96" s="61"/>
-      <c r="Z96" s="61"/>
-      <c r="AA96" s="61"/>
-    </row>
-    <row r="97" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B97" s="61"/>
-      <c r="C97" s="61"/>
-      <c r="D97" s="61"/>
-      <c r="G97" s="77"/>
-      <c r="H97" s="77"/>
-      <c r="I97" s="61"/>
-      <c r="J97" s="61"/>
-      <c r="K97" s="61"/>
-      <c r="L97" s="61"/>
-      <c r="M97" s="61"/>
-      <c r="N97" s="61"/>
-      <c r="O97" s="61"/>
-      <c r="P97" s="61"/>
-      <c r="Q97" s="61"/>
-      <c r="R97" s="61"/>
-      <c r="S97" s="61"/>
-      <c r="T97" s="61"/>
-      <c r="U97" s="61"/>
-      <c r="V97" s="61"/>
-      <c r="W97" s="61"/>
-      <c r="X97" s="61"/>
-      <c r="Y97" s="61"/>
-      <c r="Z97" s="61"/>
-      <c r="AA97" s="61"/>
-    </row>
-    <row r="98" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="G98" s="77"/>
-      <c r="H98" s="77"/>
-      <c r="I98" s="61"/>
-      <c r="J98" s="61"/>
-      <c r="K98" s="61"/>
-      <c r="L98" s="61"/>
-      <c r="M98" s="61"/>
-      <c r="N98" s="61"/>
-      <c r="O98" s="61"/>
-      <c r="P98" s="61"/>
-      <c r="Q98" s="61"/>
-      <c r="R98" s="61"/>
-      <c r="S98" s="61"/>
-      <c r="T98" s="61"/>
-      <c r="U98" s="61"/>
-      <c r="V98" s="61"/>
-      <c r="W98" s="61"/>
-      <c r="X98" s="61"/>
-      <c r="Y98" s="61"/>
-      <c r="Z98" s="61"/>
-      <c r="AA98" s="61"/>
-    </row>
-    <row r="99" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B99" s="61"/>
-      <c r="C99" s="61"/>
-      <c r="D99" s="61"/>
-      <c r="G99" s="77"/>
-      <c r="H99" s="77"/>
-      <c r="I99" s="61"/>
-      <c r="J99" s="61"/>
-      <c r="K99" s="61"/>
-      <c r="L99" s="61"/>
-      <c r="M99" s="61"/>
-      <c r="N99" s="61"/>
-      <c r="O99" s="61"/>
-      <c r="P99" s="61"/>
-      <c r="Q99" s="61"/>
-      <c r="R99" s="61"/>
-      <c r="S99" s="61"/>
-      <c r="T99" s="61"/>
-      <c r="U99" s="61"/>
-      <c r="V99" s="61"/>
-      <c r="W99" s="61"/>
-      <c r="X99" s="61"/>
-      <c r="Y99" s="61"/>
-      <c r="Z99" s="61"/>
-      <c r="AA99" s="61"/>
-    </row>
-    <row r="100" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B100" s="61"/>
-      <c r="C100" s="61"/>
-      <c r="D100" s="61"/>
-      <c r="G100" s="77"/>
-      <c r="H100" s="77"/>
-      <c r="I100" s="61"/>
-      <c r="J100" s="61"/>
-      <c r="K100" s="61"/>
-      <c r="L100" s="61"/>
-      <c r="M100" s="61"/>
-      <c r="N100" s="61"/>
-      <c r="O100" s="61"/>
-      <c r="P100" s="61"/>
-      <c r="Q100" s="61"/>
-      <c r="R100" s="61"/>
-      <c r="S100" s="61"/>
-      <c r="T100" s="61"/>
-      <c r="U100" s="61"/>
-      <c r="V100" s="61"/>
-      <c r="W100" s="61"/>
-      <c r="X100" s="61"/>
-      <c r="Y100" s="61"/>
-      <c r="Z100" s="61"/>
-      <c r="AA100" s="61"/>
-    </row>
-    <row r="101" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B101" s="61"/>
-      <c r="C101" s="61"/>
-      <c r="D101" s="61"/>
-      <c r="G101" s="77"/>
-      <c r="H101" s="77"/>
-      <c r="I101" s="61"/>
-      <c r="J101" s="61"/>
-      <c r="K101" s="61"/>
-      <c r="L101" s="61"/>
-      <c r="M101" s="61"/>
-      <c r="N101" s="61"/>
-      <c r="O101" s="61"/>
-      <c r="P101" s="61"/>
-      <c r="Q101" s="61"/>
-      <c r="R101" s="61"/>
-      <c r="S101" s="61"/>
-      <c r="T101" s="61"/>
-      <c r="U101" s="61"/>
-      <c r="V101" s="61"/>
-      <c r="W101" s="61"/>
-      <c r="X101" s="61"/>
-      <c r="Y101" s="61"/>
-      <c r="Z101" s="61"/>
-      <c r="AA101" s="61"/>
-    </row>
-    <row r="102" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B102" s="61"/>
-      <c r="C102" s="61"/>
-      <c r="D102" s="61"/>
-      <c r="G102" s="77"/>
-      <c r="H102" s="77"/>
-      <c r="I102" s="61"/>
-      <c r="J102" s="61"/>
-      <c r="K102" s="61"/>
-      <c r="L102" s="61"/>
-      <c r="M102" s="61"/>
-      <c r="N102" s="61"/>
-      <c r="O102" s="61"/>
-      <c r="P102" s="61"/>
-      <c r="Q102" s="61"/>
-      <c r="R102" s="61"/>
-      <c r="S102" s="61"/>
-      <c r="T102" s="61"/>
-      <c r="U102" s="61"/>
-      <c r="V102" s="61"/>
-      <c r="W102" s="61"/>
-      <c r="X102" s="61"/>
-      <c r="Y102" s="61"/>
-      <c r="Z102" s="61"/>
-      <c r="AA102" s="61"/>
-    </row>
-    <row r="103" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B103" s="61"/>
-      <c r="C103" s="61"/>
-      <c r="D103" s="61"/>
-      <c r="G103" s="77"/>
-      <c r="H103" s="77"/>
-      <c r="I103" s="61"/>
-      <c r="J103" s="61"/>
-      <c r="K103" s="61"/>
-      <c r="L103" s="61"/>
-      <c r="M103" s="61"/>
-      <c r="N103" s="61"/>
-      <c r="O103" s="61"/>
-      <c r="P103" s="61"/>
-      <c r="Q103" s="61"/>
-      <c r="R103" s="61"/>
-      <c r="S103" s="61"/>
-      <c r="T103" s="61"/>
-      <c r="U103" s="61"/>
-      <c r="V103" s="61"/>
-      <c r="W103" s="61"/>
-      <c r="X103" s="61"/>
-      <c r="Y103" s="61"/>
-      <c r="Z103" s="61"/>
-      <c r="AA103" s="61"/>
-    </row>
-    <row r="104" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B104" s="61"/>
-      <c r="C104" s="61"/>
-      <c r="D104" s="61"/>
-      <c r="G104" s="77"/>
-      <c r="H104" s="77"/>
-      <c r="I104" s="61"/>
-      <c r="J104" s="61"/>
-      <c r="K104" s="61"/>
-      <c r="L104" s="61"/>
-      <c r="M104" s="61"/>
-      <c r="N104" s="61"/>
-      <c r="O104" s="61"/>
-      <c r="P104" s="61"/>
-      <c r="Q104" s="61"/>
-      <c r="R104" s="61"/>
-      <c r="S104" s="61"/>
-      <c r="T104" s="61"/>
-      <c r="U104" s="61"/>
-      <c r="V104" s="61"/>
-      <c r="W104" s="61"/>
-      <c r="X104" s="61"/>
-      <c r="Y104" s="61"/>
-      <c r="Z104" s="61"/>
-      <c r="AA104" s="61"/>
-    </row>
-    <row r="105" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B105" s="61"/>
-      <c r="C105" s="61"/>
-      <c r="D105" s="61"/>
-      <c r="G105" s="77"/>
-      <c r="H105" s="77"/>
-      <c r="I105" s="61"/>
-      <c r="J105" s="61"/>
-      <c r="K105" s="61"/>
-      <c r="L105" s="61"/>
-      <c r="M105" s="61"/>
-      <c r="N105" s="61"/>
-      <c r="O105" s="61"/>
-      <c r="P105" s="61"/>
-      <c r="Q105" s="61"/>
-      <c r="R105" s="61"/>
-      <c r="S105" s="61"/>
-      <c r="T105" s="61"/>
-      <c r="U105" s="61"/>
-      <c r="V105" s="61"/>
-      <c r="W105" s="61"/>
-      <c r="X105" s="61"/>
-      <c r="Y105" s="61"/>
-      <c r="Z105" s="61"/>
-      <c r="AA105" s="61"/>
-    </row>
-    <row r="106" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B106" s="61"/>
-      <c r="C106" s="61"/>
-      <c r="D106" s="61"/>
-      <c r="G106" s="77"/>
-      <c r="H106" s="77"/>
-      <c r="I106" s="61"/>
-      <c r="J106" s="61"/>
-      <c r="K106" s="61"/>
-      <c r="L106" s="61"/>
-      <c r="M106" s="61"/>
-      <c r="N106" s="61"/>
-      <c r="O106" s="61"/>
-      <c r="P106" s="61"/>
-      <c r="Q106" s="61"/>
-      <c r="R106" s="61"/>
-      <c r="S106" s="61"/>
-      <c r="T106" s="61"/>
-      <c r="U106" s="61"/>
-      <c r="V106" s="61"/>
-      <c r="W106" s="61"/>
-      <c r="X106" s="61"/>
-      <c r="Y106" s="61"/>
-      <c r="Z106" s="61"/>
-      <c r="AA106" s="61"/>
-    </row>
-    <row r="107" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B107" s="61"/>
-      <c r="C107" s="61"/>
-      <c r="D107" s="61"/>
-      <c r="G107" s="77"/>
-      <c r="H107" s="77"/>
-      <c r="I107" s="61"/>
-      <c r="J107" s="61"/>
-      <c r="K107" s="61"/>
-      <c r="L107" s="61"/>
-      <c r="M107" s="61"/>
-      <c r="N107" s="61"/>
-      <c r="O107" s="61"/>
-      <c r="P107" s="61"/>
-      <c r="Q107" s="61"/>
-      <c r="R107" s="61"/>
-      <c r="S107" s="61"/>
-      <c r="T107" s="61"/>
-      <c r="U107" s="61"/>
-      <c r="V107" s="61"/>
-      <c r="W107" s="61"/>
-      <c r="X107" s="61"/>
-      <c r="Y107" s="61"/>
-      <c r="Z107" s="61"/>
-      <c r="AA107" s="61"/>
-    </row>
-    <row r="108" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B108" s="61"/>
-      <c r="C108" s="61"/>
-      <c r="D108" s="61"/>
-      <c r="G108" s="77"/>
-      <c r="H108" s="77"/>
-      <c r="I108" s="61"/>
-      <c r="J108" s="61"/>
-      <c r="K108" s="61"/>
-      <c r="L108" s="61"/>
-      <c r="M108" s="61"/>
-      <c r="N108" s="61"/>
-      <c r="O108" s="61"/>
-      <c r="P108" s="61"/>
-      <c r="Q108" s="61"/>
-      <c r="R108" s="61"/>
-      <c r="S108" s="61"/>
-      <c r="T108" s="61"/>
-      <c r="U108" s="61"/>
-      <c r="V108" s="61"/>
-      <c r="W108" s="61"/>
-      <c r="X108" s="61"/>
-      <c r="Y108" s="61"/>
-      <c r="Z108" s="61"/>
-      <c r="AA108" s="61"/>
-    </row>
-    <row r="109" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B109" s="61"/>
-      <c r="C109" s="61"/>
-      <c r="D109" s="61"/>
-      <c r="G109" s="77"/>
-      <c r="H109" s="77"/>
-      <c r="I109" s="61"/>
-      <c r="J109" s="61"/>
-      <c r="K109" s="61"/>
-      <c r="L109" s="61"/>
-      <c r="M109" s="61"/>
-      <c r="N109" s="61"/>
-      <c r="O109" s="61"/>
-      <c r="P109" s="61"/>
-      <c r="Q109" s="61"/>
-      <c r="R109" s="61"/>
-      <c r="S109" s="61"/>
-      <c r="T109" s="61"/>
-      <c r="U109" s="61"/>
-      <c r="V109" s="61"/>
-      <c r="W109" s="61"/>
-      <c r="X109" s="61"/>
-      <c r="Y109" s="61"/>
-      <c r="Z109" s="61"/>
-      <c r="AA109" s="61"/>
-    </row>
-    <row r="110" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B110" s="61"/>
-      <c r="C110" s="61"/>
-      <c r="D110" s="61"/>
-      <c r="G110" s="77"/>
-      <c r="H110" s="77"/>
-      <c r="I110" s="61"/>
-      <c r="J110" s="61"/>
-      <c r="K110" s="61"/>
-      <c r="L110" s="61"/>
-      <c r="M110" s="61"/>
-      <c r="N110" s="61"/>
-      <c r="O110" s="61"/>
-      <c r="P110" s="61"/>
-      <c r="Q110" s="61"/>
-      <c r="R110" s="61"/>
-      <c r="S110" s="61"/>
-      <c r="T110" s="61"/>
-      <c r="U110" s="61"/>
-      <c r="V110" s="61"/>
-      <c r="W110" s="61"/>
-      <c r="X110" s="61"/>
-      <c r="Y110" s="61"/>
-      <c r="Z110" s="61"/>
-      <c r="AA110" s="61"/>
-    </row>
-    <row r="111" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B111" s="61"/>
-      <c r="C111" s="61"/>
-      <c r="D111" s="61"/>
-      <c r="G111" s="77"/>
-      <c r="H111" s="77"/>
-      <c r="I111" s="61"/>
-      <c r="J111" s="61"/>
-      <c r="K111" s="61"/>
-      <c r="L111" s="61"/>
-      <c r="M111" s="61"/>
-      <c r="N111" s="61"/>
-      <c r="O111" s="61"/>
-      <c r="P111" s="61"/>
-      <c r="Q111" s="61"/>
-      <c r="R111" s="61"/>
-      <c r="S111" s="61"/>
-      <c r="T111" s="61"/>
-      <c r="U111" s="61"/>
-      <c r="V111" s="61"/>
-      <c r="W111" s="61"/>
-      <c r="X111" s="61"/>
-      <c r="Y111" s="61"/>
-      <c r="Z111" s="61"/>
-      <c r="AA111" s="61"/>
-    </row>
-    <row r="112" spans="2:27" ht="15" hidden="1" customHeight="1">
-      <c r="B112" s="61"/>
-      <c r="C112" s="61"/>
-      <c r="D112" s="61"/>
-      <c r="G112" s="77"/>
-      <c r="H112" s="77"/>
-      <c r="I112" s="61"/>
-      <c r="J112" s="61"/>
-      <c r="K112" s="61"/>
-      <c r="L112" s="61"/>
-      <c r="M112" s="61"/>
-      <c r="N112" s="61"/>
-      <c r="O112" s="61"/>
-      <c r="P112" s="61"/>
-      <c r="Q112" s="61"/>
-      <c r="R112" s="61"/>
-      <c r="S112" s="61"/>
-      <c r="T112" s="61"/>
-      <c r="U112" s="61"/>
-      <c r="V112" s="61"/>
-      <c r="W112" s="61"/>
-      <c r="X112" s="61"/>
-      <c r="Y112" s="61"/>
-      <c r="Z112" s="61"/>
-      <c r="AA112" s="61"/>
-    </row>
-    <row r="113" spans="2:27" ht="15" customHeight="1">
-      <c r="B113" s="61"/>
-      <c r="C113" s="61"/>
-      <c r="D113" s="61"/>
-      <c r="G113" s="61"/>
-      <c r="H113" s="61"/>
-      <c r="I113" s="61"/>
-      <c r="J113" s="61"/>
-      <c r="K113" s="61"/>
-      <c r="L113" s="61"/>
-      <c r="M113" s="61"/>
-      <c r="N113" s="61"/>
-      <c r="O113" s="61"/>
-      <c r="P113" s="61"/>
-      <c r="Q113" s="61"/>
-      <c r="R113" s="61"/>
-      <c r="S113" s="61"/>
-      <c r="T113" s="61"/>
-      <c r="U113" s="61"/>
-      <c r="V113" s="61"/>
-      <c r="W113" s="61"/>
-      <c r="X113" s="61"/>
-      <c r="Y113" s="61"/>
-      <c r="Z113" s="61"/>
-      <c r="AA113" s="61"/>
-    </row>
-    <row r="114" spans="2:27" ht="15" customHeight="1">
-      <c r="B114" s="61"/>
-      <c r="C114" s="61"/>
-      <c r="D114" s="61"/>
-      <c r="G114" s="61"/>
-      <c r="H114" s="61"/>
-      <c r="I114" s="61"/>
-      <c r="J114" s="61"/>
-      <c r="K114" s="61"/>
-      <c r="L114" s="61"/>
-      <c r="M114" s="61"/>
-      <c r="N114" s="61"/>
-      <c r="O114" s="61"/>
-      <c r="P114" s="61"/>
-      <c r="Q114" s="61"/>
-      <c r="R114" s="61"/>
-      <c r="S114" s="61"/>
-      <c r="T114" s="61"/>
-      <c r="U114" s="61"/>
-      <c r="V114" s="61"/>
-      <c r="W114" s="61"/>
-      <c r="X114" s="61"/>
-      <c r="Y114" s="61"/>
-      <c r="Z114" s="61"/>
-      <c r="AA114" s="61"/>
-    </row>
+    <row r="84" spans="2:28" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="111"/>
+      <c r="H84" s="111"/>
+    </row>
+    <row r="85" spans="2:28" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="111"/>
+      <c r="H85" s="111"/>
+    </row>
+    <row r="86" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G86" s="111"/>
+      <c r="H86" s="111"/>
+    </row>
+    <row r="87" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G87" s="111"/>
+      <c r="H87" s="111"/>
+    </row>
+    <row r="88" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G88" s="111"/>
+      <c r="H88" s="111"/>
+    </row>
+    <row r="89" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G89" s="111"/>
+      <c r="H89" s="111"/>
+    </row>
+    <row r="90" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G90" s="111"/>
+      <c r="H90" s="111"/>
+    </row>
+    <row r="91" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G91" s="111"/>
+      <c r="H91" s="111"/>
+    </row>
+    <row r="92" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G92" s="111"/>
+      <c r="H92" s="111"/>
+    </row>
+    <row r="93" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G93" s="111"/>
+      <c r="H93" s="111"/>
+    </row>
+    <row r="94" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G94" s="111"/>
+      <c r="H94" s="111"/>
+    </row>
+    <row r="95" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G95" s="111"/>
+      <c r="H95" s="111"/>
+    </row>
+    <row r="96" spans="2:28" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G96" s="111"/>
+      <c r="H96" s="111"/>
+    </row>
+    <row r="97" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G97" s="111"/>
+      <c r="H97" s="111"/>
+    </row>
+    <row r="98" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G98" s="111"/>
+      <c r="H98" s="111"/>
+    </row>
+    <row r="99" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G99" s="111"/>
+      <c r="H99" s="111"/>
+    </row>
+    <row r="100" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G100" s="111"/>
+      <c r="H100" s="111"/>
+    </row>
+    <row r="101" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G101" s="111"/>
+      <c r="H101" s="111"/>
+    </row>
+    <row r="102" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G102" s="111"/>
+      <c r="H102" s="111"/>
+    </row>
+    <row r="103" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G103" s="111"/>
+      <c r="H103" s="111"/>
+    </row>
+    <row r="104" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G104" s="111"/>
+      <c r="H104" s="111"/>
+    </row>
+    <row r="105" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G105" s="111"/>
+      <c r="H105" s="111"/>
+    </row>
+    <row r="106" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G106" s="111"/>
+      <c r="H106" s="111"/>
+    </row>
+    <row r="107" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G107" s="111"/>
+      <c r="H107" s="111"/>
+    </row>
+    <row r="108" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G108" s="111"/>
+      <c r="H108" s="111"/>
+    </row>
+    <row r="109" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G109" s="111"/>
+      <c r="H109" s="111"/>
+    </row>
+    <row r="110" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G110" s="111"/>
+      <c r="H110" s="111"/>
+    </row>
+    <row r="111" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G111" s="111"/>
+      <c r="H111" s="111"/>
+    </row>
+    <row r="112" spans="7:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G112" s="111"/>
+      <c r="H112" s="111"/>
+    </row>
+    <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="B80:I80"/>
-    <mergeCell ref="B81:I81"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B59:I59"/>
-    <mergeCell ref="B67:I67"/>
-    <mergeCell ref="B60:I61"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="B77:I78"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="B55:C56"/>
-    <mergeCell ref="D55:E56"/>
-    <mergeCell ref="B47:C48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="B49:C50"/>
-    <mergeCell ref="D49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="D45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="B53:C54"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="B45:C46"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B51:C52"/>
-    <mergeCell ref="D51:E52"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="E11:I11"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="G92:H92"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:I42"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="H39:I40"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="B69:E70"/>
+    <mergeCell ref="H73:I74"/>
+    <mergeCell ref="B73:E74"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="I64:I65"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="G87:H87"/>
     <mergeCell ref="G110:H110"/>
     <mergeCell ref="G83:H83"/>
     <mergeCell ref="G84:H84"/>
@@ -8119,50 +7269,151 @@
     <mergeCell ref="E64:F65"/>
     <mergeCell ref="G104:H104"/>
     <mergeCell ref="G95:H95"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:I42"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="H39:I40"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="B82:I82"/>
-    <mergeCell ref="B69:E70"/>
-    <mergeCell ref="H73:I74"/>
-    <mergeCell ref="B73:E74"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="I64:I65"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="G92:H92"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="D45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B53:C54"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="B45:C46"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B51:C52"/>
+    <mergeCell ref="D51:E52"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="B67:I67"/>
+    <mergeCell ref="B60:I61"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="B77:I78"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="B55:C56"/>
+    <mergeCell ref="D55:E56"/>
+    <mergeCell ref="B47:C48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="B49:C50"/>
+    <mergeCell ref="D49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
     <mergeCell ref="I49:I50"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
-  <conditionalFormatting sqref="B11:I11 B15:I15 B17:I17 B19:I19 B21:I21 B29:I29 H39:I40 B69:E70 B25:I25">
-    <cfRule type="containsBlanks" dxfId="10" priority="5">
+  <conditionalFormatting sqref="B47:D47 F47:I47 B48:C48 F48:H48">
+    <cfRule type="containsBlanks" dxfId="3" priority="2">
+      <formula>LEN(TRIM(B47))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:H56">
+    <cfRule type="containsBlanks" dxfId="2" priority="1">
+      <formula>LEN(TRIM(B49))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:I11 B15:I15 B17:I17 B19:I19 B21:I21 B25:I25 B29:I29 H39:I40 B69:E70">
+    <cfRule type="containsBlanks" dxfId="1" priority="5">
       <formula>LEN(TRIM(B11))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F47:I47 B47:D47 F48:H48 B49:H54 B48:C48">
-    <cfRule type="containsBlanks" dxfId="9" priority="2">
-      <formula>LEN(TRIM(B47))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G64:G65 I64:I65 B65:D65 H70">
-    <cfRule type="containsBlanks" dxfId="8" priority="6">
+    <cfRule type="containsBlanks" dxfId="0" priority="6">
       <formula>LEN(TRIM(B64))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55:H56">
-    <cfRule type="containsBlanks" dxfId="7" priority="1">
-      <formula>LEN(TRIM(B55))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="1156" yWindow="532" count="34">
@@ -8233,17 +7484,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2B5944-189C-4F5D-9CE2-C4B36B6B91BB}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="58.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="58.6640625" customWidth="1"/>
     <col min="3" max="3" width="133" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>111</v>
       </c>
@@ -8254,7 +7505,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="25.5" thickBot="1">
+    <row r="2" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="53" t="s">
         <v>30</v>
       </c>
@@ -8293,7 +7544,7 @@
         <v>592375 - 01 PLANEAR ACTIVIDADES DE ANÁLISIS DE ACUERDO CON LA METODOLOGÍA SELECCIONADA</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="25.5" thickBot="1">
+    <row r="3" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="53" t="s">
         <v>30</v>
       </c>
@@ -8325,7 +7576,7 @@
         <v>592374 - 04 VERIFICAR LOS MODELOS REALIZADOS EN LA FASE DE ANÁLISIS DE ACUERDO CON LO ESTABLECIDO EN EL INFORME DE REQUISITOS</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="25.5" thickBot="1">
+    <row r="4" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="53" t="s">
         <v>30</v>
       </c>
@@ -8351,7 +7602,7 @@
         <v>592376 - 03 DESARROLLAR PROCESOS LÓGICOS A TRAVÉS DE LA IMPLEMENTACIÓN DE ALGORITMOS</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="25.5" thickBot="1">
+    <row r="5" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="53" t="s">
         <v>30</v>
       </c>
@@ -8377,7 +7628,7 @@
         <v>592373 - 02 MODELAR LAS FUNCIONES DEL SOFTWARE DE ACUERDO CON EL INFORME DE REQUISITOS</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="25.5" thickBot="1">
+    <row r="6" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="53" t="s">
         <v>30</v>
       </c>
@@ -8394,7 +7645,7 @@
         <v>593105 - 05 REALIZAR PRUEBAS AL SOFTWARE PARA VERIFICAR SU FUNCIONALIDAD</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="25.5" thickBot="1">
+    <row r="7" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="53" t="s">
         <v>30</v>
       </c>
@@ -8408,7 +7659,7 @@
         <v>38367 - Estructurar propuesta técnica de servicio de tecnología de la información según requisitos técnicos y normativa</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="25.5" thickBot="1">
+    <row r="8" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="53" t="s">
         <v>30</v>
       </c>
@@ -8422,7 +7673,7 @@
         <v>38356 - Implementar la solución de software de acuerdo con los requisitos de operación y modelos de referencia</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="25.5" thickBot="1">
+    <row r="9" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="53" t="s">
         <v>30</v>
       </c>
@@ -8433,7 +7684,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="25.5" thickBot="1">
+    <row r="10" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="53" t="s">
         <v>30</v>
       </c>
@@ -8444,7 +7695,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="25.5" thickBot="1">
+    <row r="11" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="53" t="s">
         <v>30</v>
       </c>
@@ -8455,7 +7706,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="25.5" thickBot="1">
+    <row r="12" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="53" t="s">
         <v>30</v>
       </c>
@@ -8466,7 +7717,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="25.5" thickBot="1">
+    <row r="13" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="53" t="s">
         <v>30</v>
       </c>
@@ -8477,7 +7728,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="25.5" thickBot="1">
+    <row r="14" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="53" t="s">
         <v>30</v>
       </c>
@@ -8488,7 +7739,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="25.5" thickBot="1">
+    <row r="15" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="53" t="s">
         <v>30</v>
       </c>
@@ -8499,7 +7750,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="25.5" thickBot="1">
+    <row r="16" spans="1:11" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="53" t="s">
         <v>30</v>
       </c>
@@ -8510,7 +7761,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="25.5" thickBot="1">
+    <row r="17" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="53" t="s">
         <v>30</v>
       </c>
@@ -8521,7 +7772,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="25.5" thickBot="1">
+    <row r="18" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="53" t="s">
         <v>30</v>
       </c>
@@ -8532,7 +7783,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="25.5" thickBot="1">
+    <row r="19" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="53" t="s">
         <v>30</v>
       </c>
@@ -8543,7 +7794,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="25.5" thickBot="1">
+    <row r="20" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="53" t="s">
         <v>30</v>
       </c>
@@ -8554,7 +7805,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="25.5" thickBot="1">
+    <row r="21" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="53" t="s">
         <v>30</v>
       </c>
@@ -8565,7 +7816,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="25.5" thickBot="1">
+    <row r="22" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="53" t="s">
         <v>30</v>
       </c>
@@ -8576,7 +7827,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="25.5" thickBot="1">
+    <row r="23" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="53" t="s">
         <v>30</v>
       </c>
@@ -8587,7 +7838,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="25.5" thickBot="1">
+    <row r="24" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="53" t="s">
         <v>30</v>
       </c>
@@ -8598,7 +7849,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="25.5" thickBot="1">
+    <row r="25" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="53" t="s">
         <v>30</v>
       </c>
@@ -8609,7 +7860,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="25.5" thickBot="1">
+    <row r="26" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="53" t="s">
         <v>30</v>
       </c>
@@ -8620,7 +7871,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="25.5" thickBot="1">
+    <row r="27" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="53" t="s">
         <v>30</v>
       </c>
@@ -8631,7 +7882,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="25.5" thickBot="1">
+    <row r="28" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="53" t="s">
         <v>144</v>
       </c>
@@ -8642,7 +7893,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="25.5" thickBot="1">
+    <row r="29" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="53" t="s">
         <v>144</v>
       </c>
@@ -8653,7 +7904,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="25.5" thickBot="1">
+    <row r="30" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="53" t="s">
         <v>144</v>
       </c>
@@ -8664,7 +7915,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="25.5" thickBot="1">
+    <row r="31" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="53" t="s">
         <v>144</v>
       </c>
@@ -8675,7 +7926,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="25.5" thickBot="1">
+    <row r="32" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="53" t="s">
         <v>144</v>
       </c>
@@ -8686,7 +7937,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="25.5" thickBot="1">
+    <row r="33" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="53" t="s">
         <v>144</v>
       </c>
@@ -8697,7 +7948,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="25.5" thickBot="1">
+    <row r="34" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="53" t="s">
         <v>144</v>
       </c>
@@ -8708,7 +7959,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="25.5" thickBot="1">
+    <row r="35" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="53" t="s">
         <v>144</v>
       </c>
@@ -8719,7 +7970,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="25.5" thickBot="1">
+    <row r="36" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="53" t="s">
         <v>144</v>
       </c>
@@ -8730,7 +7981,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="25.5" thickBot="1">
+    <row r="37" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="53" t="s">
         <v>144</v>
       </c>
@@ -8741,7 +7992,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="25.5" thickBot="1">
+    <row r="38" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="53" t="s">
         <v>144</v>
       </c>
@@ -8752,7 +8003,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="24.95">
+    <row r="39" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A39" s="55" t="s">
         <v>144</v>
       </c>
@@ -8774,64 +8025,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D237D29B-37DE-45D6-8EA7-98C4A952DFFE}">
   <dimension ref="D1:D12"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="4:4">
+    <row r="1" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="4:4">
+    <row r="2" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="4:4">
+    <row r="3" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="4:4">
+    <row r="4" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="4:4">
+    <row r="5" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="4:4">
+    <row r="6" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="4:4">
+    <row r="7" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D7">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="4:4">
+    <row r="8" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D8">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="4:4">
+    <row r="9" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="4:4">
+    <row r="10" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="4:4">
+    <row r="11" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D11">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="4:4">
+    <row r="12" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D12">
         <v>12</v>
       </c>
@@ -8844,134 +8095,134 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="20" width="5.7109375" style="1" customWidth="1"/>
-    <col min="21" max="24" width="8.42578125" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="20" width="5.6640625" style="1" customWidth="1"/>
+    <col min="21" max="24" width="8.44140625" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="18.600000000000001">
-      <c r="A1" s="250" t="s">
+    <row r="1" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="310" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="250"/>
-      <c r="C1" s="250"/>
-      <c r="D1" s="250"/>
-      <c r="E1" s="250"/>
-      <c r="F1" s="250"/>
-      <c r="G1" s="250"/>
-      <c r="H1" s="250"/>
-      <c r="I1" s="250"/>
-      <c r="J1" s="250"/>
-      <c r="K1" s="250"/>
-      <c r="L1" s="250"/>
-      <c r="M1" s="250"/>
-      <c r="N1" s="250"/>
-      <c r="O1" s="250"/>
-      <c r="P1" s="250"/>
-      <c r="Q1" s="250"/>
-      <c r="R1" s="250"/>
-      <c r="S1" s="250"/>
-      <c r="T1" s="250"/>
-      <c r="U1" s="250" t="s">
+      <c r="B1" s="310"/>
+      <c r="C1" s="310"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
+      <c r="J1" s="310"/>
+      <c r="K1" s="310"/>
+      <c r="L1" s="310"/>
+      <c r="M1" s="310"/>
+      <c r="N1" s="310"/>
+      <c r="O1" s="310"/>
+      <c r="P1" s="310"/>
+      <c r="Q1" s="310"/>
+      <c r="R1" s="310"/>
+      <c r="S1" s="310"/>
+      <c r="T1" s="310"/>
+      <c r="U1" s="310" t="s">
         <v>163</v>
       </c>
-      <c r="V1" s="250"/>
-      <c r="W1" s="250"/>
-      <c r="X1" s="250"/>
-    </row>
-    <row r="2" spans="1:24" ht="33" customHeight="1">
-      <c r="A2" s="250"/>
-      <c r="B2" s="250"/>
-      <c r="C2" s="250"/>
-      <c r="D2" s="250"/>
-      <c r="E2" s="250"/>
-      <c r="F2" s="250"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="250"/>
-      <c r="J2" s="250"/>
-      <c r="K2" s="250"/>
-      <c r="L2" s="250"/>
-      <c r="M2" s="250"/>
-      <c r="N2" s="250"/>
-      <c r="O2" s="250"/>
-      <c r="P2" s="250"/>
-      <c r="Q2" s="250"/>
-      <c r="R2" s="250"/>
-      <c r="S2" s="250"/>
-      <c r="T2" s="250"/>
-      <c r="U2" s="258" t="s">
+      <c r="V1" s="310"/>
+      <c r="W1" s="310"/>
+      <c r="X1" s="310"/>
+    </row>
+    <row r="2" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="310"/>
+      <c r="B2" s="310"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="310"/>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
+      <c r="G2" s="310"/>
+      <c r="H2" s="310"/>
+      <c r="I2" s="310"/>
+      <c r="J2" s="310"/>
+      <c r="K2" s="310"/>
+      <c r="L2" s="310"/>
+      <c r="M2" s="310"/>
+      <c r="N2" s="310"/>
+      <c r="O2" s="310"/>
+      <c r="P2" s="310"/>
+      <c r="Q2" s="310"/>
+      <c r="R2" s="310"/>
+      <c r="S2" s="310"/>
+      <c r="T2" s="310"/>
+      <c r="U2" s="290" t="s">
         <v>164</v>
       </c>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258"/>
-    </row>
-    <row r="3" spans="1:24" ht="33" customHeight="1" thickBot="1">
-      <c r="U3" s="259"/>
-      <c r="V3" s="259"/>
-      <c r="W3" s="259"/>
-      <c r="X3" s="259"/>
-    </row>
-    <row r="4" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="255" t="s">
+      <c r="V2" s="290"/>
+      <c r="W2" s="290"/>
+      <c r="X2" s="290"/>
+    </row>
+    <row r="3" spans="1:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U3" s="317"/>
+      <c r="V3" s="317"/>
+      <c r="W3" s="317"/>
+      <c r="X3" s="317"/>
+    </row>
+    <row r="4" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="314" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="256"/>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="256"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="256"/>
-      <c r="L4" s="256"/>
-      <c r="M4" s="257"/>
-      <c r="N4" s="255" t="s">
+      <c r="B4" s="315"/>
+      <c r="C4" s="315"/>
+      <c r="D4" s="315"/>
+      <c r="E4" s="315"/>
+      <c r="F4" s="315"/>
+      <c r="G4" s="315"/>
+      <c r="H4" s="315"/>
+      <c r="I4" s="315"/>
+      <c r="J4" s="315"/>
+      <c r="K4" s="315"/>
+      <c r="L4" s="315"/>
+      <c r="M4" s="316"/>
+      <c r="N4" s="314" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="256"/>
-      <c r="P4" s="256"/>
-      <c r="Q4" s="256"/>
-      <c r="R4" s="256"/>
-      <c r="S4" s="256"/>
-      <c r="T4" s="256"/>
-      <c r="U4" s="256"/>
-      <c r="V4" s="256"/>
-      <c r="W4" s="256"/>
-      <c r="X4" s="257"/>
-    </row>
-    <row r="5" spans="1:24" ht="18" customHeight="1" thickBot="1">
-      <c r="A5" s="252"/>
-      <c r="B5" s="253"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="253"/>
-      <c r="E5" s="253"/>
-      <c r="F5" s="253"/>
-      <c r="G5" s="253"/>
-      <c r="H5" s="253"/>
-      <c r="I5" s="253"/>
-      <c r="J5" s="253"/>
-      <c r="K5" s="253"/>
-      <c r="L5" s="253"/>
-      <c r="M5" s="254"/>
-      <c r="N5" s="252"/>
-      <c r="O5" s="253"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="254"/>
-    </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
+      <c r="O4" s="315"/>
+      <c r="P4" s="315"/>
+      <c r="Q4" s="315"/>
+      <c r="R4" s="315"/>
+      <c r="S4" s="315"/>
+      <c r="T4" s="315"/>
+      <c r="U4" s="315"/>
+      <c r="V4" s="315"/>
+      <c r="W4" s="315"/>
+      <c r="X4" s="316"/>
+    </row>
+    <row r="5" spans="1:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="311"/>
+      <c r="B5" s="312"/>
+      <c r="C5" s="312"/>
+      <c r="D5" s="312"/>
+      <c r="E5" s="312"/>
+      <c r="F5" s="312"/>
+      <c r="G5" s="312"/>
+      <c r="H5" s="312"/>
+      <c r="I5" s="312"/>
+      <c r="J5" s="312"/>
+      <c r="K5" s="312"/>
+      <c r="L5" s="312"/>
+      <c r="M5" s="313"/>
+      <c r="N5" s="311"/>
+      <c r="O5" s="312"/>
+      <c r="P5" s="312"/>
+      <c r="Q5" s="312"/>
+      <c r="R5" s="312"/>
+      <c r="S5" s="312"/>
+      <c r="T5" s="312"/>
+      <c r="U5" s="312"/>
+      <c r="V5" s="312"/>
+      <c r="W5" s="312"/>
+      <c r="X5" s="313"/>
+    </row>
+    <row r="6" spans="1:24" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -8997,69 +8248,69 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="251" t="s">
+    <row r="7" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="288" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="251"/>
-      <c r="C7" s="251"/>
-      <c r="D7" s="251"/>
-      <c r="E7" s="251"/>
-      <c r="F7" s="251"/>
-      <c r="G7" s="251"/>
-      <c r="H7" s="251"/>
-      <c r="I7" s="251"/>
-      <c r="J7" s="251" t="s">
+      <c r="B7" s="288"/>
+      <c r="C7" s="288"/>
+      <c r="D7" s="288"/>
+      <c r="E7" s="288"/>
+      <c r="F7" s="288"/>
+      <c r="G7" s="288"/>
+      <c r="H7" s="288"/>
+      <c r="I7" s="288"/>
+      <c r="J7" s="288" t="s">
         <v>168</v>
       </c>
-      <c r="K7" s="251"/>
-      <c r="L7" s="251"/>
-      <c r="M7" s="251"/>
-      <c r="N7" s="251"/>
-      <c r="O7" s="251"/>
-      <c r="P7" s="251" t="s">
+      <c r="K7" s="288"/>
+      <c r="L7" s="288"/>
+      <c r="M7" s="288"/>
+      <c r="N7" s="288"/>
+      <c r="O7" s="288"/>
+      <c r="P7" s="288" t="s">
         <v>169</v>
       </c>
-      <c r="Q7" s="251"/>
-      <c r="R7" s="251"/>
-      <c r="S7" s="251"/>
-      <c r="T7" s="251"/>
-      <c r="U7" s="251"/>
-      <c r="V7" s="251"/>
-      <c r="W7" s="251"/>
-      <c r="X7" s="251"/>
-    </row>
-    <row r="8" spans="1:24" ht="18" customHeight="1">
-      <c r="A8" s="260"/>
-      <c r="B8" s="260"/>
-      <c r="C8" s="260"/>
-      <c r="D8" s="260"/>
-      <c r="E8" s="260"/>
-      <c r="F8" s="260"/>
-      <c r="G8" s="260"/>
-      <c r="H8" s="260"/>
-      <c r="I8" s="260"/>
-      <c r="J8" s="261" t="s">
+      <c r="Q7" s="288"/>
+      <c r="R7" s="288"/>
+      <c r="S7" s="288"/>
+      <c r="T7" s="288"/>
+      <c r="U7" s="288"/>
+      <c r="V7" s="288"/>
+      <c r="W7" s="288"/>
+      <c r="X7" s="288"/>
+    </row>
+    <row r="8" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="295"/>
+      <c r="B8" s="295"/>
+      <c r="C8" s="295"/>
+      <c r="D8" s="295"/>
+      <c r="E8" s="295"/>
+      <c r="F8" s="295"/>
+      <c r="G8" s="295"/>
+      <c r="H8" s="295"/>
+      <c r="I8" s="295"/>
+      <c r="J8" s="296" t="s">
         <v>170</v>
       </c>
-      <c r="K8" s="262"/>
-      <c r="L8" s="262"/>
-      <c r="M8" s="262"/>
-      <c r="N8" s="262"/>
-      <c r="O8" s="263"/>
-      <c r="P8" s="261" t="s">
+      <c r="K8" s="297"/>
+      <c r="L8" s="297"/>
+      <c r="M8" s="297"/>
+      <c r="N8" s="297"/>
+      <c r="O8" s="298"/>
+      <c r="P8" s="296" t="s">
         <v>171</v>
       </c>
-      <c r="Q8" s="262"/>
-      <c r="R8" s="262"/>
-      <c r="S8" s="262"/>
-      <c r="T8" s="262"/>
-      <c r="U8" s="262"/>
-      <c r="V8" s="262"/>
-      <c r="W8" s="262"/>
-      <c r="X8" s="263"/>
-    </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
+      <c r="Q8" s="297"/>
+      <c r="R8" s="297"/>
+      <c r="S8" s="297"/>
+      <c r="T8" s="297"/>
+      <c r="U8" s="297"/>
+      <c r="V8" s="297"/>
+      <c r="W8" s="297"/>
+      <c r="X8" s="298"/>
+    </row>
+    <row r="9" spans="1:24" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -9085,69 +8336,69 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:24" ht="18" customHeight="1">
-      <c r="A10" s="264" t="s">
+    <row r="10" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="308" t="s">
         <v>172</v>
       </c>
-      <c r="B10" s="264"/>
-      <c r="C10" s="264"/>
-      <c r="D10" s="264"/>
-      <c r="E10" s="264"/>
-      <c r="F10" s="264"/>
-      <c r="G10" s="264"/>
-      <c r="H10" s="264"/>
-      <c r="I10" s="264"/>
-      <c r="J10" s="264"/>
-      <c r="K10" s="264"/>
-      <c r="L10" s="264"/>
-      <c r="M10" s="264"/>
-      <c r="N10" s="264"/>
-      <c r="O10" s="264"/>
-      <c r="P10" s="264"/>
-      <c r="Q10" s="264"/>
-      <c r="R10" s="264"/>
-      <c r="S10" s="264"/>
-      <c r="T10" s="264"/>
-      <c r="U10" s="264"/>
-      <c r="V10" s="264"/>
-      <c r="W10" s="264"/>
-      <c r="X10" s="264"/>
-    </row>
-    <row r="11" spans="1:24" ht="18" customHeight="1">
-      <c r="A11" s="265" t="s">
+      <c r="B10" s="308"/>
+      <c r="C10" s="308"/>
+      <c r="D10" s="308"/>
+      <c r="E10" s="308"/>
+      <c r="F10" s="308"/>
+      <c r="G10" s="308"/>
+      <c r="H10" s="308"/>
+      <c r="I10" s="308"/>
+      <c r="J10" s="308"/>
+      <c r="K10" s="308"/>
+      <c r="L10" s="308"/>
+      <c r="M10" s="308"/>
+      <c r="N10" s="308"/>
+      <c r="O10" s="308"/>
+      <c r="P10" s="308"/>
+      <c r="Q10" s="308"/>
+      <c r="R10" s="308"/>
+      <c r="S10" s="308"/>
+      <c r="T10" s="308"/>
+      <c r="U10" s="308"/>
+      <c r="V10" s="308"/>
+      <c r="W10" s="308"/>
+      <c r="X10" s="308"/>
+    </row>
+    <row r="11" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="309" t="s">
         <v>173</v>
       </c>
-      <c r="B11" s="265"/>
-      <c r="C11" s="265"/>
-      <c r="D11" s="265"/>
-      <c r="E11" s="265"/>
-      <c r="F11" s="265"/>
-      <c r="G11" s="265" t="s">
+      <c r="B11" s="309"/>
+      <c r="C11" s="309"/>
+      <c r="D11" s="309"/>
+      <c r="E11" s="309"/>
+      <c r="F11" s="309"/>
+      <c r="G11" s="309" t="s">
         <v>174</v>
       </c>
-      <c r="H11" s="265"/>
-      <c r="I11" s="265"/>
-      <c r="J11" s="265"/>
-      <c r="K11" s="265"/>
-      <c r="L11" s="265"/>
-      <c r="M11" s="265" t="s">
+      <c r="H11" s="309"/>
+      <c r="I11" s="309"/>
+      <c r="J11" s="309"/>
+      <c r="K11" s="309"/>
+      <c r="L11" s="309"/>
+      <c r="M11" s="309" t="s">
         <v>175</v>
       </c>
-      <c r="N11" s="265"/>
-      <c r="O11" s="265"/>
-      <c r="P11" s="265"/>
-      <c r="Q11" s="265"/>
-      <c r="R11" s="265"/>
-      <c r="S11" s="265" t="s">
+      <c r="N11" s="309"/>
+      <c r="O11" s="309"/>
+      <c r="P11" s="309"/>
+      <c r="Q11" s="309"/>
+      <c r="R11" s="309"/>
+      <c r="S11" s="309" t="s">
         <v>176</v>
       </c>
-      <c r="T11" s="265"/>
-      <c r="U11" s="265"/>
-      <c r="V11" s="265"/>
-      <c r="W11" s="265"/>
-      <c r="X11" s="265"/>
-    </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
+      <c r="T11" s="309"/>
+      <c r="U11" s="309"/>
+      <c r="V11" s="309"/>
+      <c r="W11" s="309"/>
+      <c r="X11" s="309"/>
+    </row>
+    <row r="12" spans="1:24" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -9173,69 +8424,69 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="A13" s="251" t="s">
+    <row r="13" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="288" t="s">
         <v>177</v>
       </c>
-      <c r="B13" s="251"/>
-      <c r="C13" s="251"/>
-      <c r="D13" s="251"/>
-      <c r="E13" s="251"/>
-      <c r="F13" s="251"/>
-      <c r="G13" s="251"/>
-      <c r="H13" s="251"/>
-      <c r="I13" s="251"/>
-      <c r="J13" s="251" t="s">
+      <c r="B13" s="288"/>
+      <c r="C13" s="288"/>
+      <c r="D13" s="288"/>
+      <c r="E13" s="288"/>
+      <c r="F13" s="288"/>
+      <c r="G13" s="288"/>
+      <c r="H13" s="288"/>
+      <c r="I13" s="288"/>
+      <c r="J13" s="288" t="s">
         <v>168</v>
       </c>
-      <c r="K13" s="251"/>
-      <c r="L13" s="251"/>
-      <c r="M13" s="251"/>
-      <c r="N13" s="251"/>
-      <c r="O13" s="251"/>
-      <c r="P13" s="251" t="s">
+      <c r="K13" s="288"/>
+      <c r="L13" s="288"/>
+      <c r="M13" s="288"/>
+      <c r="N13" s="288"/>
+      <c r="O13" s="288"/>
+      <c r="P13" s="288" t="s">
         <v>169</v>
       </c>
-      <c r="Q13" s="251"/>
-      <c r="R13" s="251"/>
-      <c r="S13" s="251"/>
-      <c r="T13" s="251"/>
-      <c r="U13" s="251"/>
-      <c r="V13" s="251"/>
-      <c r="W13" s="251"/>
-      <c r="X13" s="251"/>
-    </row>
-    <row r="14" spans="1:24" ht="18" customHeight="1">
-      <c r="A14" s="260"/>
-      <c r="B14" s="260"/>
-      <c r="C14" s="260"/>
-      <c r="D14" s="260"/>
-      <c r="E14" s="260"/>
-      <c r="F14" s="260"/>
-      <c r="G14" s="260"/>
-      <c r="H14" s="260"/>
-      <c r="I14" s="260"/>
-      <c r="J14" s="261" t="s">
+      <c r="Q13" s="288"/>
+      <c r="R13" s="288"/>
+      <c r="S13" s="288"/>
+      <c r="T13" s="288"/>
+      <c r="U13" s="288"/>
+      <c r="V13" s="288"/>
+      <c r="W13" s="288"/>
+      <c r="X13" s="288"/>
+    </row>
+    <row r="14" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="295"/>
+      <c r="B14" s="295"/>
+      <c r="C14" s="295"/>
+      <c r="D14" s="295"/>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
+      <c r="G14" s="295"/>
+      <c r="H14" s="295"/>
+      <c r="I14" s="295"/>
+      <c r="J14" s="296" t="s">
         <v>178</v>
       </c>
-      <c r="K14" s="262"/>
-      <c r="L14" s="262"/>
-      <c r="M14" s="262"/>
-      <c r="N14" s="262"/>
-      <c r="O14" s="263"/>
-      <c r="P14" s="261" t="s">
+      <c r="K14" s="297"/>
+      <c r="L14" s="297"/>
+      <c r="M14" s="297"/>
+      <c r="N14" s="297"/>
+      <c r="O14" s="298"/>
+      <c r="P14" s="296" t="s">
         <v>179</v>
       </c>
-      <c r="Q14" s="262"/>
-      <c r="R14" s="262"/>
-      <c r="S14" s="262"/>
-      <c r="T14" s="262"/>
-      <c r="U14" s="262"/>
-      <c r="V14" s="262"/>
-      <c r="W14" s="262"/>
-      <c r="X14" s="263"/>
-    </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
+      <c r="Q14" s="297"/>
+      <c r="R14" s="297"/>
+      <c r="S14" s="297"/>
+      <c r="T14" s="297"/>
+      <c r="U14" s="297"/>
+      <c r="V14" s="297"/>
+      <c r="W14" s="297"/>
+      <c r="X14" s="298"/>
+    </row>
+    <row r="15" spans="1:24" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -9261,173 +8512,185 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
     </row>
-    <row r="16" spans="1:24" s="4" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="271" t="s">
+    <row r="16" spans="1:24" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="299" t="s">
         <v>180</v>
       </c>
-      <c r="B16" s="271"/>
-      <c r="C16" s="271"/>
-      <c r="D16" s="271"/>
-      <c r="E16" s="271"/>
-      <c r="F16" s="271"/>
-      <c r="G16" s="271"/>
-      <c r="H16" s="271"/>
-      <c r="I16" s="271"/>
-      <c r="J16" s="272" t="s">
+      <c r="B16" s="299"/>
+      <c r="C16" s="299"/>
+      <c r="D16" s="299"/>
+      <c r="E16" s="299"/>
+      <c r="F16" s="299"/>
+      <c r="G16" s="299"/>
+      <c r="H16" s="299"/>
+      <c r="I16" s="299"/>
+      <c r="J16" s="300" t="s">
         <v>181</v>
       </c>
-      <c r="K16" s="272"/>
-      <c r="L16" s="272"/>
-      <c r="M16" s="272"/>
-      <c r="N16" s="271" t="s">
+      <c r="K16" s="300"/>
+      <c r="L16" s="300"/>
+      <c r="M16" s="300"/>
+      <c r="N16" s="299" t="s">
         <v>182</v>
       </c>
-      <c r="O16" s="271"/>
-      <c r="P16" s="271"/>
-      <c r="Q16" s="271"/>
-      <c r="R16" s="271"/>
-      <c r="S16" s="271"/>
-      <c r="T16" s="273" t="s">
+      <c r="O16" s="299"/>
+      <c r="P16" s="299"/>
+      <c r="Q16" s="299"/>
+      <c r="R16" s="299"/>
+      <c r="S16" s="299"/>
+      <c r="T16" s="301" t="s">
         <v>183</v>
       </c>
-      <c r="U16" s="273"/>
-      <c r="V16" s="273"/>
-      <c r="W16" s="273"/>
-      <c r="X16" s="273"/>
-    </row>
-    <row r="17" spans="1:24" ht="18" customHeight="1">
-      <c r="A17" s="266" t="s">
+      <c r="U16" s="301"/>
+      <c r="V16" s="301"/>
+      <c r="W16" s="301"/>
+      <c r="X16" s="301"/>
+    </row>
+    <row r="17" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="289" t="s">
         <v>184</v>
       </c>
-      <c r="B17" s="258"/>
-      <c r="C17" s="258"/>
-      <c r="D17" s="258"/>
-      <c r="E17" s="258"/>
-      <c r="F17" s="258"/>
-      <c r="G17" s="258"/>
-      <c r="H17" s="258"/>
-      <c r="I17" s="267"/>
-      <c r="J17" s="274" t="s">
+      <c r="B17" s="290"/>
+      <c r="C17" s="290"/>
+      <c r="D17" s="290"/>
+      <c r="E17" s="290"/>
+      <c r="F17" s="290"/>
+      <c r="G17" s="290"/>
+      <c r="H17" s="290"/>
+      <c r="I17" s="291"/>
+      <c r="J17" s="302" t="s">
         <v>185</v>
       </c>
-      <c r="K17" s="275"/>
-      <c r="L17" s="275"/>
-      <c r="M17" s="276"/>
-      <c r="N17" s="266" t="s">
+      <c r="K17" s="303"/>
+      <c r="L17" s="303"/>
+      <c r="M17" s="304"/>
+      <c r="N17" s="289" t="s">
         <v>186</v>
       </c>
-      <c r="O17" s="258"/>
-      <c r="P17" s="258"/>
-      <c r="Q17" s="258"/>
-      <c r="R17" s="258"/>
-      <c r="S17" s="267"/>
-      <c r="T17" s="266" t="s">
+      <c r="O17" s="290"/>
+      <c r="P17" s="290"/>
+      <c r="Q17" s="290"/>
+      <c r="R17" s="290"/>
+      <c r="S17" s="291"/>
+      <c r="T17" s="289" t="s">
         <v>187</v>
       </c>
-      <c r="U17" s="258"/>
-      <c r="V17" s="258"/>
-      <c r="W17" s="258"/>
-      <c r="X17" s="267"/>
-    </row>
-    <row r="18" spans="1:24" ht="48.75" customHeight="1">
-      <c r="A18" s="268"/>
-      <c r="B18" s="269"/>
-      <c r="C18" s="269"/>
-      <c r="D18" s="269"/>
-      <c r="E18" s="269"/>
-      <c r="F18" s="269"/>
-      <c r="G18" s="269"/>
-      <c r="H18" s="269"/>
-      <c r="I18" s="270"/>
-      <c r="J18" s="277"/>
-      <c r="K18" s="278"/>
-      <c r="L18" s="278"/>
-      <c r="M18" s="279"/>
-      <c r="N18" s="268"/>
-      <c r="O18" s="269"/>
-      <c r="P18" s="269"/>
-      <c r="Q18" s="269"/>
-      <c r="R18" s="269"/>
-      <c r="S18" s="270"/>
-      <c r="T18" s="268"/>
-      <c r="U18" s="269"/>
-      <c r="V18" s="269"/>
-      <c r="W18" s="269"/>
-      <c r="X18" s="270"/>
-    </row>
-    <row r="19" spans="1:24" ht="39" customHeight="1"/>
-    <row r="20" spans="1:24" ht="39" customHeight="1"/>
-    <row r="21" spans="1:24">
-      <c r="A21" s="283" t="s">
+      <c r="U17" s="290"/>
+      <c r="V17" s="290"/>
+      <c r="W17" s="290"/>
+      <c r="X17" s="291"/>
+    </row>
+    <row r="18" spans="1:24" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="292"/>
+      <c r="B18" s="293"/>
+      <c r="C18" s="293"/>
+      <c r="D18" s="293"/>
+      <c r="E18" s="293"/>
+      <c r="F18" s="293"/>
+      <c r="G18" s="293"/>
+      <c r="H18" s="293"/>
+      <c r="I18" s="294"/>
+      <c r="J18" s="305"/>
+      <c r="K18" s="306"/>
+      <c r="L18" s="306"/>
+      <c r="M18" s="307"/>
+      <c r="N18" s="292"/>
+      <c r="O18" s="293"/>
+      <c r="P18" s="293"/>
+      <c r="Q18" s="293"/>
+      <c r="R18" s="293"/>
+      <c r="S18" s="294"/>
+      <c r="T18" s="292"/>
+      <c r="U18" s="293"/>
+      <c r="V18" s="293"/>
+      <c r="W18" s="293"/>
+      <c r="X18" s="294"/>
+    </row>
+    <row r="19" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A21" s="287" t="s">
         <v>188</v>
       </c>
-      <c r="B21" s="283"/>
-      <c r="C21" s="283"/>
-      <c r="D21" s="283"/>
-      <c r="E21" s="283"/>
-      <c r="F21" s="283"/>
-      <c r="G21" s="283"/>
-      <c r="H21" s="283"/>
+      <c r="B21" s="287"/>
+      <c r="C21" s="287"/>
+      <c r="D21" s="287"/>
+      <c r="E21" s="287"/>
+      <c r="F21" s="287"/>
+      <c r="G21" s="287"/>
+      <c r="H21" s="287"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="283" t="s">
+      <c r="J21" s="287" t="s">
         <v>104</v>
       </c>
-      <c r="K21" s="283"/>
-      <c r="L21" s="283"/>
-      <c r="M21" s="283"/>
-      <c r="N21" s="283"/>
-      <c r="O21" s="283"/>
-      <c r="P21" s="283"/>
+      <c r="K21" s="287"/>
+      <c r="L21" s="287"/>
+      <c r="M21" s="287"/>
+      <c r="N21" s="287"/>
+      <c r="O21" s="287"/>
+      <c r="P21" s="287"/>
       <c r="Q21" s="6"/>
-      <c r="R21" s="283" t="s">
+      <c r="R21" s="287" t="s">
         <v>189</v>
       </c>
-      <c r="S21" s="283"/>
-      <c r="T21" s="283"/>
-      <c r="U21" s="283"/>
-      <c r="V21" s="283"/>
-      <c r="W21" s="283"/>
-      <c r="X21" s="283"/>
-    </row>
-    <row r="23" spans="1:24" ht="38.25" customHeight="1">
-      <c r="P23" s="280" t="s">
+      <c r="S21" s="287"/>
+      <c r="T21" s="287"/>
+      <c r="U21" s="287"/>
+      <c r="V21" s="287"/>
+      <c r="W21" s="287"/>
+      <c r="X21" s="287"/>
+    </row>
+    <row r="23" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P23" s="284" t="s">
         <v>190</v>
       </c>
-      <c r="Q23" s="280"/>
-      <c r="R23" s="280"/>
-      <c r="S23" s="280"/>
-      <c r="T23" s="280"/>
-      <c r="U23" s="281" t="s">
+      <c r="Q23" s="284"/>
+      <c r="R23" s="284"/>
+      <c r="S23" s="284"/>
+      <c r="T23" s="284"/>
+      <c r="U23" s="285" t="s">
         <v>191</v>
       </c>
-      <c r="V23" s="281"/>
-      <c r="W23" s="281"/>
-      <c r="X23" s="281"/>
-    </row>
-    <row r="24" spans="1:24" ht="38.25" customHeight="1">
-      <c r="P24" s="280" t="s">
+      <c r="V23" s="285"/>
+      <c r="W23" s="285"/>
+      <c r="X23" s="285"/>
+    </row>
+    <row r="24" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P24" s="284" t="s">
         <v>192</v>
       </c>
-      <c r="Q24" s="280"/>
-      <c r="R24" s="280"/>
-      <c r="S24" s="280"/>
-      <c r="T24" s="280"/>
-      <c r="U24" s="282" t="s">
+      <c r="Q24" s="284"/>
+      <c r="R24" s="284"/>
+      <c r="S24" s="284"/>
+      <c r="T24" s="284"/>
+      <c r="U24" s="286" t="s">
         <v>193</v>
       </c>
-      <c r="V24" s="282"/>
-      <c r="W24" s="282"/>
-      <c r="X24" s="282"/>
+      <c r="V24" s="286"/>
+      <c r="W24" s="286"/>
+      <c r="X24" s="286"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="P23:T23"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="P24:T24"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="R21:X21"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P7:X7"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:X4"/>
+    <mergeCell ref="N5:X5"/>
+    <mergeCell ref="U2:X3"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="A10:X10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="M11:R11"/>
+    <mergeCell ref="S11:X11"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="J13:O13"/>
     <mergeCell ref="P13:X13"/>
@@ -9442,25 +8705,13 @@
     <mergeCell ref="T16:X16"/>
     <mergeCell ref="A17:I18"/>
     <mergeCell ref="J17:M18"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="P8:X8"/>
-    <mergeCell ref="A10:X10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="M11:R11"/>
-    <mergeCell ref="S11:X11"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:X7"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="N4:X4"/>
-    <mergeCell ref="N5:X5"/>
-    <mergeCell ref="U2:X3"/>
+    <mergeCell ref="P23:T23"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="P24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="R21:X21"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="95" orientation="landscape" horizontalDpi="4294967294" verticalDpi="200" r:id="rId1"/>
@@ -9469,6 +8720,37 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="41dd0a9e-964d-48c8-9389-7445c2a187f7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edbb1c21-1b45-407e-8894-c97732534993">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="edbb1c21-1b45-407e-8894-c97732534993" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_x0031_010005470 xmlns="edbb1c21-1b45-407e-8894-c97732534993">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_x0031_010005470>
+    <FechayHora xmlns="edbb1c21-1b45-407e-8894-c97732534993" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010080239B14884FBB46AB47CE62E6B5D997" ma:contentTypeVersion="24" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="95cfff668db4ca1e5f6e9375137a4a8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="edbb1c21-1b45-407e-8894-c97732534993" xmlns:ns3="41dd0a9e-964d-48c8-9389-7445c2a187f7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6912f17aaadcd6a9684df23b147afc35" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9778,45 +9060,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="41dd0a9e-964d-48c8-9389-7445c2a187f7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edbb1c21-1b45-407e-8894-c97732534993">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="edbb1c21-1b45-407e-8894-c97732534993" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_x0031_010005470 xmlns="edbb1c21-1b45-407e-8894-c97732534993">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_x0031_010005470>
-    <FechayHora xmlns="edbb1c21-1b45-407e-8894-c97732534993" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DC6A2-D4C3-4E6B-B67E-9AED22EC483E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAD99F47-C05E-4B8B-A445-C498A7984441}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="41dd0a9e-964d-48c8-9389-7445c2a187f7"/>
+    <ds:schemaRef ds:uri="edbb1c21-1b45-407e-8894-c97732534993"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FFAC935-8881-451D-93ED-25958414B4DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FFAC935-8881-451D-93ED-25958414B4DF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAD99F47-C05E-4B8B-A445-C498A7984441}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DC6A2-D4C3-4E6B-B67E-9AED22EC483E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="edbb1c21-1b45-407e-8894-c97732534993"/>
+    <ds:schemaRef ds:uri="41dd0a9e-964d-48c8-9389-7445c2a187f7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>